--- a/data/BALSU (TRY).xlsx
+++ b/data/BALSU (TRY).xlsx
@@ -403,13 +403,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:F108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -417,15 +418,18 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -439,16 +443,19 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>212349113</v>
+        <v>345252409</v>
       </c>
       <c r="C3">
-        <v>608045415.3010851</v>
+        <v>233673644.50068444</v>
       </c>
       <c r="D3">
-        <v>586764338</v>
+        <v>669106577.4093287</v>
       </c>
       <c r="E3">
-        <v>549794165.9114033</v>
+        <v>645688410</v>
+      </c>
+      <c r="F3">
+        <v>605005618.6188617</v>
       </c>
     </row>
     <row r="4">
@@ -461,16 +468,19 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B5">
-        <v>28792310</v>
+        <v>29835156</v>
       </c>
       <c r="C5">
-        <v>29272294.859406274</v>
+        <v>31683692.558176596</v>
       </c>
       <c r="D5">
-        <v>349292725</v>
+        <v>32211878.477194835</v>
       </c>
       <c r="E5">
-        <v>38908617.598176345</v>
+        <v>384369413</v>
+      </c>
+      <c r="F5">
+        <v>42815900.42078176</v>
       </c>
     </row>
     <row r="6">
@@ -483,16 +493,19 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>3340403687</v>
+        <v>8266375868</v>
       </c>
       <c r="C7">
-        <v>1472741945.2117295</v>
+        <v>3675853845.665998</v>
       </c>
       <c r="D7">
-        <v>3999418661</v>
+        <v>1620637698.3861108</v>
       </c>
       <c r="E7">
-        <v>1384297342.86101</v>
+        <v>4401048449</v>
+      </c>
+      <c r="F7">
+        <v>1523311308.4816406</v>
       </c>
     </row>
     <row r="8">
@@ -510,16 +523,19 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>642166024</v>
+        <v>143655913</v>
       </c>
       <c r="C10">
-        <v>107741936.89988478</v>
+        <v>706653647.3010556</v>
       </c>
       <c r="D10">
-        <v>180192014</v>
+        <v>118561602.1902519</v>
       </c>
       <c r="E10">
-        <v>99909539.68498836</v>
+        <v>198287264</v>
+      </c>
+      <c r="F10">
+        <v>109942659.65489101</v>
       </c>
     </row>
     <row r="11">
@@ -542,16 +558,19 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
-        <v>13873510255</v>
+        <v>10707645145</v>
       </c>
       <c r="C14">
-        <v>14312038041.228127</v>
+        <v>15266716481.662298</v>
       </c>
       <c r="D14">
-        <v>6947152998</v>
+        <v>15749282123.56702</v>
       </c>
       <c r="E14">
-        <v>3704330985.8221006</v>
+        <v>7644800287</v>
+      </c>
+      <c r="F14">
+        <v>4076327466.9005256</v>
       </c>
     </row>
     <row r="15">
@@ -569,16 +588,19 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>1255546061</v>
+        <v>1837706017</v>
       </c>
       <c r="C17">
-        <v>1015680233.13722</v>
+        <v>1381630560.0125048</v>
       </c>
       <c r="D17">
-        <v>393943978</v>
+        <v>1117676915.9590464</v>
       </c>
       <c r="E17">
-        <v>133473530.24042438</v>
+        <v>433504636</v>
+      </c>
+      <c r="F17">
+        <v>146877214.67267102</v>
       </c>
     </row>
     <row r="18">
@@ -601,16 +623,19 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>87080419</v>
+        <v>127966801</v>
       </c>
       <c r="C21">
-        <v>83295241.56274018</v>
+        <v>95825212.47628967</v>
       </c>
       <c r="D21">
-        <v>52423575</v>
+        <v>91659919.79222623</v>
       </c>
       <c r="E21">
-        <v>30142959.32152469</v>
+        <v>57688060</v>
+      </c>
+      <c r="F21">
+        <v>33169976.842316985</v>
       </c>
     </row>
     <row r="22">
@@ -628,16 +653,19 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>19439847869</v>
+        <v>21458437309</v>
       </c>
       <c r="C24">
-        <v>17628815108.20019</v>
+        <v>21392037084.177006</v>
       </c>
       <c r="D24">
-        <v>12509188289</v>
+        <v>19399136715.781178</v>
       </c>
       <c r="E24">
-        <v>5940857141.439629</v>
+        <v>13765386519</v>
+      </c>
+      <c r="F24">
+        <v>6537450145.591689</v>
       </c>
     </row>
     <row r="25">
@@ -650,16 +678,19 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B26">
-        <v>46257716</v>
+        <v>46557343</v>
       </c>
       <c r="C26">
-        <v>2983657.799704207</v>
+        <v>50903010.289464325</v>
       </c>
       <c r="D26">
-        <v>2983658</v>
+        <v>3283282.8079662155</v>
       </c>
       <c r="E26">
-        <v>2983657.8155432176</v>
+        <v>3283283</v>
+      </c>
+      <c r="F26">
+        <v>3283282.825395812</v>
       </c>
     </row>
     <row r="27">
@@ -676,7 +707,7 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>0</v>
       </c>
     </row>
@@ -685,16 +716,19 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B30">
-        <v>7104514</v>
+        <v>7161255</v>
       </c>
       <c r="C30">
-        <v>7457316.1957222875</v>
+        <v>7817963.801836722</v>
       </c>
       <c r="D30">
-        <v>7657433</v>
+        <v>8206195.11440298</v>
       </c>
       <c r="E30">
-        <v>6989652.703812373</v>
+        <v>8426408</v>
+      </c>
+      <c r="F30">
+        <v>7691567.899762784</v>
       </c>
     </row>
     <row r="31">
@@ -742,16 +776,19 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>3957200486</v>
+        <v>4489439842</v>
       </c>
       <c r="C39">
-        <v>3664635435.92552</v>
+        <v>4354590638.593813</v>
       </c>
       <c r="D39">
-        <v>3015016618</v>
+        <v>4032645608.8331795</v>
       </c>
       <c r="E39">
-        <v>2240864538.7322783</v>
+        <v>3317790743</v>
+      </c>
+      <c r="F39">
+        <v>2465896731.0963836</v>
       </c>
     </row>
     <row r="40">
@@ -759,16 +796,19 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
-        <v>15699075</v>
+        <v>19736785</v>
       </c>
       <c r="C40">
-        <v>16628704.52641645</v>
+        <v>17275608.165783025</v>
       </c>
       <c r="D40">
-        <v>9101458</v>
+        <v>18298592.987354554</v>
       </c>
       <c r="E40">
-        <v>6489986.643084507</v>
+        <v>10015445</v>
+      </c>
+      <c r="F40">
+        <v>7141724.353001274</v>
       </c>
     </row>
     <row r="41">
@@ -776,16 +816,19 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
-        <v>15455713</v>
+        <v>26257136</v>
       </c>
       <c r="C41">
-        <v>18953997.735580094</v>
+        <v>17007807.256847862</v>
       </c>
       <c r="D41">
-        <v>22476688</v>
+        <v>20857396.888353005</v>
       </c>
       <c r="E41">
-        <v>42336469.76760521</v>
+        <v>24733843</v>
+      </c>
+      <c r="F41">
+        <v>46587984.504033946</v>
       </c>
     </row>
     <row r="42">
@@ -793,16 +836,19 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B42">
-        <v>22027346</v>
+        <v>27323254</v>
       </c>
       <c r="C42">
-        <v>5136981.94684042</v>
+        <v>24239377.060631156</v>
       </c>
       <c r="D42">
-        <v>29277852</v>
+        <v>5652848.162602978</v>
       </c>
       <c r="E42">
-        <v>463150.4965567003</v>
+        <v>32217993</v>
+      </c>
+      <c r="F42">
+        <v>509661.01507900277</v>
       </c>
     </row>
     <row r="43">
@@ -810,16 +856,19 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
       <c r="B43">
-        <v>818056975</v>
+        <v>794048122</v>
       </c>
       <c r="C43">
-        <v>752156615.2729462</v>
+        <v>900207926.7336298</v>
       </c>
       <c r="D43">
-        <v>649562085</v>
+        <v>827689718.3278016</v>
       </c>
       <c r="E43">
-        <v>768218787.3793759</v>
+        <v>714792436</v>
+      </c>
+      <c r="F43">
+        <v>845364886.5528116</v>
       </c>
     </row>
     <row r="44">
@@ -842,16 +891,19 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>4881801825</v>
+        <v>5410523737</v>
       </c>
       <c r="C47">
-        <v>4467952709.40273</v>
+        <v>5372042331.902005</v>
       </c>
       <c r="D47">
-        <v>3736075792</v>
+        <v>4916633643.121661</v>
       </c>
       <c r="E47">
-        <v>3068346243.538256</v>
+        <v>4111260151</v>
+      </c>
+      <c r="F47">
+        <v>3376475838.246468</v>
       </c>
     </row>
     <row r="48">
@@ -859,16 +911,19 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>24321649694</v>
+        <v>26868961046</v>
       </c>
       <c r="C48">
-        <v>22096767817.60292</v>
+        <v>26764079416.079014</v>
       </c>
       <c r="D48">
-        <v>16245264081</v>
+        <v>24315770358.90284</v>
       </c>
       <c r="E48">
-        <v>9009203384.977884</v>
+        <v>17876646670</v>
+      </c>
+      <c r="F48">
+        <v>9913925983.838158</v>
       </c>
     </row>
     <row r="49">
@@ -881,16 +936,19 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>11509348147</v>
+        <v>12071308349</v>
       </c>
       <c r="C50">
-        <v>11635329204.29567</v>
+        <v>12665140387.644045</v>
       </c>
       <c r="D50">
-        <v>8187987734</v>
+        <v>12803772719.94076</v>
       </c>
       <c r="E50">
-        <v>4438996543.569311</v>
+        <v>9010242181</v>
+      </c>
+      <c r="F50">
+        <v>4884769639.992714</v>
       </c>
     </row>
     <row r="51">
@@ -903,16 +961,19 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>6078984528</v>
+        <v>7295716654</v>
       </c>
       <c r="C52">
-        <v>4867899208.230454</v>
+        <v>6689448566.338174</v>
       </c>
       <c r="D52">
-        <v>1121277202</v>
+        <v>5356743585.970178</v>
       </c>
       <c r="E52">
-        <v>1568669873.01286</v>
+        <v>1233878148</v>
+      </c>
+      <c r="F52">
+        <v>1726198904.5621343</v>
       </c>
     </row>
     <row r="53">
@@ -925,16 +986,19 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>37301060</v>
+        <v>34181986</v>
       </c>
       <c r="C54">
-        <v>38362233.93715587</v>
+        <v>41046908.60629448</v>
       </c>
       <c r="D54">
-        <v>34508145</v>
+        <v>42214647.79691853</v>
       </c>
       <c r="E54">
-        <v>30077513.11835245</v>
+        <v>37973523</v>
+      </c>
+      <c r="F54">
+        <v>33097958.3977945</v>
       </c>
     </row>
     <row r="55">
@@ -942,16 +1006,19 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>27181859</v>
+        <v>57114268</v>
       </c>
       <c r="C55">
-        <v>29343662.354084376</v>
+        <v>29911516.780546803</v>
       </c>
       <c r="D55">
-        <v>17369680</v>
+        <v>32290412.841406263</v>
       </c>
       <c r="E55">
-        <v>28628505.21358036</v>
+        <v>19113978</v>
+      </c>
+      <c r="F55">
+        <v>31503438.160649005</v>
       </c>
     </row>
     <row r="56">
@@ -979,16 +1046,19 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
-        <v>245233454</v>
+        <v>128224423</v>
       </c>
       <c r="C60">
-        <v>194485512.33790782</v>
+        <v>269860298.1669669</v>
       </c>
       <c r="D60">
-        <v>204025244</v>
+        <v>214016144.58630562</v>
       </c>
       <c r="E60">
-        <v>7917680.246228653</v>
+        <v>224513876</v>
+      </c>
+      <c r="F60">
+        <v>8712789.862829924</v>
       </c>
     </row>
     <row r="61">
@@ -1001,16 +1071,19 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>13684248</v>
+        <v>11069894</v>
       </c>
       <c r="C62">
-        <v>15691769.92462625</v>
+        <v>15058448.12458059</v>
       </c>
       <c r="D62">
-        <v>13392350</v>
+        <v>17267569.49982478</v>
       </c>
       <c r="E62">
-        <v>6032409.568838856</v>
+        <v>14737236</v>
+      </c>
+      <c r="F62">
+        <v>6638196.454681579</v>
       </c>
     </row>
     <row r="63">
@@ -1033,16 +1106,19 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>17911733296</v>
+        <v>19597615574</v>
       </c>
       <c r="C66">
-        <v>16781111591.079897</v>
+        <v>19710466125.660606</v>
       </c>
       <c r="D66">
-        <v>9578560355</v>
+        <v>18466305080.63539</v>
       </c>
       <c r="E66">
-        <v>6080322524.729172</v>
+        <v>10540458942</v>
+      </c>
+      <c r="F66">
+        <v>6690920927.430803</v>
       </c>
     </row>
     <row r="67">
@@ -1055,16 +1131,19 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
-        <v>2020169100</v>
+        <v>2228113780</v>
       </c>
       <c r="C68">
-        <v>663426125.7469901</v>
+        <v>2223038605.7919044</v>
       </c>
       <c r="D68">
-        <v>1303929282</v>
+        <v>730048731.8742346</v>
       </c>
       <c r="E68">
-        <v>450387597.29964846</v>
+        <v>1434872523</v>
+      </c>
+      <c r="F68">
+        <v>495616439.41934186</v>
       </c>
     </row>
     <row r="69">
@@ -1127,16 +1206,19 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>52712988</v>
+        <v>24116517</v>
       </c>
       <c r="C80">
-        <v>33057908.995402735</v>
+        <v>58006533.88404238</v>
       </c>
       <c r="D80">
-        <v>33799637</v>
+        <v>36377651.71417371</v>
       </c>
       <c r="E80">
-        <v>55693146.04569675</v>
+        <v>37193866</v>
+      </c>
+      <c r="F80">
+        <v>61285965.48555793</v>
       </c>
     </row>
     <row r="81">
@@ -1149,16 +1231,19 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
-        <v>688018767</v>
+        <v>619895783</v>
       </c>
       <c r="C82">
-        <v>683764973.6672864</v>
+        <v>757111016.3749883</v>
       </c>
       <c r="D82">
-        <v>536721830</v>
+        <v>752430048.4304322</v>
       </c>
       <c r="E82">
-        <v>430006023.82593215</v>
+        <v>590620532</v>
+      </c>
+      <c r="F82">
+        <v>473188106.7224129</v>
       </c>
     </row>
     <row r="83">
@@ -1171,16 +1256,19 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>2760900855</v>
+        <v>2872126080</v>
       </c>
       <c r="C84">
-        <v>1380249008.4096792</v>
+        <v>3038156156.0509353</v>
       </c>
       <c r="D84">
-        <v>1874450749</v>
+        <v>1518856432.0188406</v>
       </c>
       <c r="E84">
-        <v>936086767.1712774</v>
+        <v>2062686921</v>
+      </c>
+      <c r="F84">
+        <v>1030090511.6273127</v>
       </c>
     </row>
     <row r="85">
@@ -1193,16 +1281,19 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>3649015543</v>
+        <v>4399219392</v>
       </c>
       <c r="C86">
-        <v>3935407218.1133456</v>
+        <v>4015457134.3674693</v>
       </c>
       <c r="D86">
-        <v>4792252977</v>
+        <v>4330608846.248609</v>
       </c>
       <c r="E86">
-        <v>1992794093.077435</v>
+        <v>5273500807</v>
+      </c>
+      <c r="F86">
+        <v>2192914544.7800407</v>
       </c>
     </row>
     <row r="87">
@@ -1219,6 +1310,9 @@
         <v>1112000000</v>
       </c>
       <c r="E87">
+        <v>1112000000</v>
+      </c>
+      <c r="F87">
         <v>76576681</v>
       </c>
     </row>
@@ -1227,16 +1321,19 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>1058329860</v>
+        <v>1276278816</v>
       </c>
       <c r="C88">
-        <v>1058329859.9574188</v>
+        <v>1276278815.9084997</v>
       </c>
       <c r="D88">
-        <v>1058329860</v>
+        <v>1276278815.8616426</v>
       </c>
       <c r="E88">
-        <v>667938981.8750515</v>
+        <v>1276278816</v>
+      </c>
+      <c r="F88">
+        <v>742704764.8888566</v>
       </c>
     </row>
     <row r="89">
@@ -1259,15 +1356,18 @@
         <v xml:space="preserve">    Geri Alınmış Paylar (-)</v>
       </c>
       <c r="B92">
-        <v>-59237107</v>
+        <v>-65185818</v>
       </c>
       <c r="C92">
-        <v>-57813080.4641158</v>
+        <v>-65185818.23493186</v>
       </c>
       <c r="D92">
-        <v>-57813080</v>
+        <v>-63618788.04674479</v>
       </c>
       <c r="E92">
+        <v>-63618788</v>
+      </c>
+      <c r="F92">
         <v>0</v>
       </c>
     </row>
@@ -1281,13 +1381,16 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>2093735178</v>
+        <v>2303992339</v>
       </c>
       <c r="C94">
-        <v>2093735177.6326199</v>
+        <v>2303992339.551469</v>
       </c>
       <c r="D94">
-        <v>2093735178</v>
+        <v>2303992339.147196</v>
+      </c>
+      <c r="E94">
+        <v>2303992339</v>
       </c>
     </row>
     <row r="95">
@@ -1305,16 +1408,19 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>39440182</v>
+        <v>49051531</v>
       </c>
       <c r="C97">
-        <v>83742001.9333278</v>
+        <v>43400845.60518175</v>
       </c>
       <c r="D97">
-        <v>67030890</v>
+        <v>92151544.75142106</v>
       </c>
       <c r="E97">
-        <v>58447882.94411861</v>
+        <v>73762269</v>
+      </c>
+      <c r="F97">
+        <v>64317338.68792562</v>
       </c>
     </row>
     <row r="98">
@@ -1322,16 +1428,19 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B98">
-        <v>-257736103</v>
+        <v>-603060672</v>
       </c>
       <c r="C98">
-        <v>-255657012.12852737</v>
+        <v>-283618488.7073853</v>
       </c>
       <c r="D98">
-        <v>-123000544</v>
+        <v>-281330611.28552336</v>
       </c>
       <c r="E98">
-        <v>-208876164.36034444</v>
+        <v>-135352509</v>
+      </c>
+      <c r="F98">
+        <v>-229851935.26758766</v>
       </c>
     </row>
     <row r="99">
@@ -1339,16 +1448,19 @@
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>96080828</v>
+        <v>105700913</v>
       </c>
       <c r="C99">
-        <v>92069614.61494942</v>
+        <v>105729460.92505415</v>
       </c>
       <c r="D99">
-        <v>92069615</v>
+        <v>101315433.30180386</v>
       </c>
       <c r="E99">
-        <v>92173590.25199781</v>
+        <v>101315433</v>
+      </c>
+      <c r="F99">
+        <v>101429850.38462152</v>
       </c>
     </row>
     <row r="100">
@@ -1371,16 +1483,19 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>743357431</v>
+        <v>818035450</v>
       </c>
       <c r="C103">
-        <v>946818458.7212775</v>
+        <v>818006902.0040411</v>
       </c>
       <c r="D103">
-        <v>414213100</v>
+        <v>1041899901.5546712</v>
       </c>
       <c r="E103">
-        <v>-26678222.49453893</v>
+        <v>455809225</v>
+      </c>
+      <c r="F103">
+        <v>-29357304.068885148</v>
       </c>
     </row>
     <row r="104">
@@ -1388,16 +1503,19 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>-780037326</v>
+        <v>-160816512</v>
       </c>
       <c r="C104">
-        <v>-740900402.6082169</v>
+        <v>-858370266.9527444</v>
       </c>
       <c r="D104">
-        <v>532605358</v>
+        <v>-815303133.8044084</v>
       </c>
       <c r="E104">
-        <v>1730128743.6095934</v>
+        <v>586090677</v>
+      </c>
+      <c r="F104">
+        <v>1903871804.6100051</v>
       </c>
     </row>
     <row r="105">
@@ -1410,16 +1528,19 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>3649015543</v>
+        <v>4399219392</v>
       </c>
       <c r="C106">
-        <v>3935407218.1133456</v>
+        <v>4015457134.3674693</v>
       </c>
       <c r="D106">
-        <v>4792252977</v>
+        <v>4330608846.248609</v>
       </c>
       <c r="E106">
-        <v>1992794093.077435</v>
+        <v>5273500807</v>
+      </c>
+      <c r="F106">
+        <v>2192914544.7800407</v>
       </c>
     </row>
     <row r="107">
@@ -1427,39 +1548,42 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>24321649694</v>
+        <v>26868961046</v>
       </c>
       <c r="C107">
-        <v>22096767817.60292</v>
+        <v>26764079416.079014</v>
       </c>
       <c r="D107">
-        <v>16245264081</v>
+        <v>24315770358.90284</v>
       </c>
       <c r="E107">
-        <v>9009203384.977884</v>
+        <v>17876646670</v>
+      </c>
+      <c r="F107">
+        <v>9913925983.838158</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
-      <c r="B108">
-        <v>-7190383587</v>
-      </c>
       <c r="C108">
-        <v>-7275200211.8518305</v>
+        <v>-7912456588.091301</v>
+      </c>
+      <c r="D108">
+        <v>-8005790671.58886</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:I50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1468,6 +1592,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1475,21 +1601,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -1503,22 +1635,28 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>6989761403</v>
+        <v>15272615607</v>
       </c>
       <c r="C3">
-        <v>2032002479</v>
+        <v>7691687514.744774</v>
       </c>
       <c r="D3">
-        <v>19512963200.439323</v>
+        <v>2236060316.8724113</v>
       </c>
       <c r="E3">
-        <v>8535074203</v>
+        <v>21472494806.48594</v>
       </c>
       <c r="F3">
-        <v>3717653550</v>
+        <v>13932819364</v>
       </c>
       <c r="G3">
-        <v>22739160575.93671</v>
+        <v>9392183781.331757</v>
+      </c>
+      <c r="H3">
+        <v>4090987910.175106</v>
+      </c>
+      <c r="I3">
+        <v>25022673509.662426</v>
       </c>
     </row>
     <row r="4">
@@ -1530,28 +1668,28 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
-      <c r="B5">
-        <v>4420870805</v>
-      </c>
       <c r="C5">
-        <v>699352685</v>
-      </c>
-      <c r="F5">
-        <v>1196473153</v>
+        <v>4864823677.747242</v>
+      </c>
+      <c r="D5">
+        <v>769583109.5620782</v>
+      </c>
+      <c r="H5">
+        <v>1316625429.9764135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="B6">
-        <v>2727221596</v>
-      </c>
       <c r="C6">
-        <v>1342320390</v>
-      </c>
-      <c r="F6">
-        <v>2387580968</v>
+        <v>3001094757.0960336</v>
+      </c>
+      <c r="D6">
+        <v>1477118944.3060215</v>
+      </c>
+      <c r="H6">
+        <v>2627346723.75595</v>
       </c>
     </row>
     <row r="7">
@@ -1559,22 +1697,28 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-6123368551</v>
+        <v>-13089206212</v>
       </c>
       <c r="C7">
-        <v>-2011008287</v>
+        <v>-6738289723.550882</v>
       </c>
       <c r="D7">
-        <v>-16494615202.915365</v>
+        <v>-2212957845.2459483</v>
       </c>
       <c r="E7">
-        <v>-7248335439</v>
+        <v>-18151038140.204662</v>
       </c>
       <c r="F7">
-        <v>-3078611482</v>
+        <v>-12541674899</v>
       </c>
       <c r="G7">
-        <v>-19525873398.24762</v>
+        <v>-7976228083.394906</v>
+      </c>
+      <c r="H7">
+        <v>-3387771932.9140463</v>
+      </c>
+      <c r="I7">
+        <v>-21486701472.718113</v>
       </c>
     </row>
     <row r="8">
@@ -1582,22 +1726,28 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>866392852</v>
+        <v>2183409395</v>
       </c>
       <c r="C8">
-        <v>20994192</v>
+        <v>953397791.1938916</v>
       </c>
       <c r="D8">
-        <v>3018347997.523956</v>
+        <v>23102471.62646313</v>
       </c>
       <c r="E8">
-        <v>1286738764</v>
+        <v>3321456666.2812743</v>
       </c>
       <c r="F8">
-        <v>639042068</v>
+        <v>1391144465</v>
       </c>
       <c r="G8">
-        <v>3213287177.689088</v>
+        <v>1415955697.9368503</v>
+      </c>
+      <c r="H8">
+        <v>703215977.2610598</v>
+      </c>
+      <c r="I8">
+        <v>3535972036.94431</v>
       </c>
     </row>
     <row r="9">
@@ -1607,11 +1757,23 @@
       <c r="B9">
         <v>0</v>
       </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1620,6 +1782,12 @@
       <c r="B11">
         <v>0</v>
       </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1631,22 +1799,28 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>866392852</v>
+        <v>2183409395</v>
       </c>
       <c r="C13">
-        <v>20994192</v>
+        <v>953397791.1938916</v>
       </c>
       <c r="D13">
-        <v>3018347997.523956</v>
+        <v>23102471.62646313</v>
       </c>
       <c r="E13">
-        <v>1286738764</v>
+        <v>3321456666.2812743</v>
       </c>
       <c r="F13">
-        <v>639042068</v>
+        <v>1391144465</v>
       </c>
       <c r="G13">
-        <v>3213287177.689088</v>
+        <v>1415955697.9368503</v>
+      </c>
+      <c r="H13">
+        <v>703215977.2610598</v>
+      </c>
+      <c r="I13">
+        <v>3535972036.94431</v>
       </c>
     </row>
     <row r="14"/>
@@ -1655,22 +1829,28 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-389392671</v>
+        <v>-557809836</v>
       </c>
       <c r="C15">
-        <v>-197167910</v>
+        <v>-428496278.0815853</v>
       </c>
       <c r="D15">
-        <v>-674454651.4450238</v>
+        <v>-216967914.09852955</v>
       </c>
       <c r="E15">
-        <v>-319320462</v>
+        <v>-742184764.6408465</v>
       </c>
       <c r="F15">
-        <v>-173761460</v>
+        <v>-463970320</v>
       </c>
       <c r="G15">
-        <v>-574117904.6768087</v>
+        <v>-351387274.7807631</v>
+      </c>
+      <c r="H15">
+        <v>-191210940.5983716</v>
+      </c>
+      <c r="I15">
+        <v>-631771996.8951621</v>
       </c>
     </row>
     <row r="16">
@@ -1678,22 +1858,28 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-158831659</v>
+        <v>-220967974</v>
       </c>
       <c r="C16">
-        <v>-66307087</v>
+        <v>-174781858.4983679</v>
       </c>
       <c r="D16">
-        <v>-329366894.21632606</v>
+        <v>-72965780.06197725</v>
       </c>
       <c r="E16">
-        <v>-180721204</v>
+        <v>-362442590.2330014</v>
       </c>
       <c r="F16">
-        <v>-79734000</v>
+        <v>-287329583</v>
       </c>
       <c r="G16">
-        <v>-389867197.7795394</v>
+        <v>-198869596.30121773</v>
+      </c>
+      <c r="H16">
+        <v>-87741051.08043268</v>
+      </c>
+      <c r="I16">
+        <v>-429018457.80921215</v>
       </c>
     </row>
     <row r="17">
@@ -1706,22 +1892,28 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>409996829</v>
+        <v>560481289</v>
       </c>
       <c r="C18">
-        <v>118824605</v>
+        <v>451169547.69739914</v>
       </c>
       <c r="D18">
-        <v>384939260.3413288</v>
+        <v>130757214.44951008</v>
       </c>
       <c r="E18">
-        <v>392169693</v>
+        <v>423595646.83162147</v>
       </c>
       <c r="F18">
-        <v>147860827</v>
+        <v>283881866</v>
       </c>
       <c r="G18">
-        <v>1322675710.0327792</v>
+        <v>431552174.3009332</v>
+      </c>
+      <c r="H18">
+        <v>162709313.14874482</v>
+      </c>
+      <c r="I18">
+        <v>1455501505.4660954</v>
       </c>
     </row>
     <row r="19">
@@ -1729,22 +1921,28 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-352801417</v>
+        <v>-480700385</v>
       </c>
       <c r="C19">
-        <v>-140895610</v>
+        <v>-388230455.6430887</v>
       </c>
       <c r="D19">
-        <v>-246056106.72261402</v>
+        <v>-155044634.83606395</v>
       </c>
       <c r="E19">
-        <v>-139605086</v>
+        <v>-270765563.35567355</v>
       </c>
       <c r="F19">
-        <v>-104919137</v>
+        <v>-191831315</v>
       </c>
       <c r="G19">
-        <v>-1343130868.8358486</v>
+        <v>-153624513.7809993</v>
+      </c>
+      <c r="H19">
+        <v>-115455330.96084374</v>
+      </c>
+      <c r="I19">
+        <v>-1478010813.081397</v>
       </c>
     </row>
     <row r="20">
@@ -1757,22 +1955,28 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>375363934</v>
+        <v>1484412489</v>
       </c>
       <c r="C21">
-        <v>-264551810</v>
+        <v>413058746.66824895</v>
       </c>
       <c r="D21">
-        <v>2153409605.4813213</v>
+        <v>-291118642.9205975</v>
       </c>
       <c r="E21">
-        <v>1039261705</v>
+        <v>2369659394.8833747</v>
       </c>
       <c r="F21">
-        <v>428488298</v>
+        <v>731895113</v>
       </c>
       <c r="G21">
-        <v>2228846916.4296703</v>
+        <v>1143626487.3748033</v>
+      </c>
+      <c r="H21">
+        <v>471517967.77015656</v>
+      </c>
+      <c r="I21">
+        <v>2452672274.6246343</v>
       </c>
     </row>
     <row r="22"/>
@@ -1791,22 +1995,28 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>13787922</v>
+        <v>49797832</v>
       </c>
       <c r="C25">
-        <v>12644343</v>
+        <v>15172533.27934158</v>
       </c>
       <c r="D25">
-        <v>82142578.88124847</v>
+        <v>13914113.741208412</v>
       </c>
       <c r="E25">
-        <v>2478115</v>
+        <v>90391504.37075894</v>
       </c>
       <c r="F25">
-        <v>1185094</v>
+        <v>33017390</v>
       </c>
       <c r="G25">
-        <v>12620282.245922156</v>
+        <v>2726972.368101267</v>
+      </c>
+      <c r="H25">
+        <v>1304103.5591982629</v>
+      </c>
+      <c r="I25">
+        <v>13887636.757078957</v>
       </c>
     </row>
     <row r="26">
@@ -1814,21 +2024,27 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-192024</v>
+        <v>-292913</v>
       </c>
       <c r="C26">
-        <v>-98416</v>
+        <v>-211307.44215352304</v>
       </c>
       <c r="D26">
-        <v>-120546.57289993837</v>
+        <v>-108299.1356652352</v>
       </c>
       <c r="E26">
-        <v>-132692</v>
+        <v>-132652.10588186464</v>
       </c>
       <c r="F26">
-        <v>-63456</v>
+        <v>-136716</v>
       </c>
       <c r="G26">
+        <v>-146017.2015697792</v>
+      </c>
+      <c r="H26">
+        <v>-69828.38108410385</v>
+      </c>
+      <c r="I26">
         <v>0</v>
       </c>
     </row>
@@ -1867,22 +2083,28 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>388959832</v>
+        <v>1533917408</v>
       </c>
       <c r="C33">
-        <v>-252005883</v>
+        <v>428019972.505437</v>
       </c>
       <c r="D33">
-        <v>2235431637.7896695</v>
+        <v>-277312828.31505436</v>
       </c>
       <c r="E33">
-        <v>1041607128</v>
+        <v>2459918247.1482515</v>
       </c>
       <c r="F33">
-        <v>429609936</v>
+        <v>764775787</v>
       </c>
       <c r="G33">
-        <v>2241467198.6755924</v>
+        <v>1146207442.5413349</v>
+      </c>
+      <c r="H33">
+        <v>472752242.94827074</v>
+      </c>
+      <c r="I33">
+        <v>2466559911.381713</v>
       </c>
     </row>
     <row r="34"/>
@@ -1891,22 +2113,28 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>122637295</v>
+        <v>240598250</v>
       </c>
       <c r="C35">
-        <v>66106560</v>
+        <v>134952782.56403908</v>
       </c>
       <c r="D35">
-        <v>409673497.1416717</v>
+        <v>72745115.73120235</v>
       </c>
       <c r="E35">
-        <v>37730125</v>
+        <v>450813746.1936804</v>
       </c>
       <c r="F35">
-        <v>18043447</v>
+        <v>416308399</v>
       </c>
       <c r="G35">
-        <v>172748437.68521506</v>
+        <v>41519061.18965699</v>
+      </c>
+      <c r="H35">
+        <v>19855406.78874859</v>
+      </c>
+      <c r="I35">
+        <v>190096188.51435268</v>
       </c>
     </row>
     <row r="36">
@@ -1914,22 +2142,28 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-1796207421</v>
+        <v>-2923879511</v>
       </c>
       <c r="C36">
-        <v>-851429657</v>
+        <v>-1976586237.7030282</v>
       </c>
       <c r="D36">
-        <v>-3106974723.744117</v>
+        <v>-936931961.6002243</v>
       </c>
       <c r="E36">
-        <v>-1074506703</v>
+        <v>-3418983469.3060145</v>
       </c>
       <c r="F36">
-        <v>-703634332</v>
+        <v>-2120810261</v>
       </c>
       <c r="G36">
-        <v>-2612395123.258974</v>
+        <v>-1182410860.0370018</v>
+      </c>
+      <c r="H36">
+        <v>-774294728.296061</v>
+      </c>
+      <c r="I36">
+        <v>-2874737175.510308</v>
       </c>
     </row>
     <row r="37">
@@ -1937,22 +2171,28 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>496571918</v>
+        <v>946803819</v>
       </c>
       <c r="C37">
-        <v>335306821</v>
+        <v>546438683.9033089</v>
       </c>
       <c r="D37">
-        <v>1216986454.0025892</v>
+        <v>368979016.59240097</v>
       </c>
       <c r="E37">
-        <v>256222623</v>
+        <v>1339198718.5496254</v>
       </c>
       <c r="F37">
-        <v>547033245</v>
+        <v>680700646</v>
       </c>
       <c r="G37">
-        <v>1474804916.2472537</v>
+        <v>281953021.95557034</v>
+      </c>
+      <c r="H37">
+        <v>601967440.3923025</v>
+      </c>
+      <c r="I37">
+        <v>1622907837.185185</v>
       </c>
     </row>
     <row r="38">
@@ -1960,22 +2200,28 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>-788038376</v>
+        <v>-202560034</v>
       </c>
       <c r="C38">
-        <v>-702022159</v>
+        <v>-867174798.7302433</v>
       </c>
       <c r="D38">
-        <v>755116865.1898141</v>
+        <v>-772520657.5916753</v>
       </c>
       <c r="E38">
-        <v>261053173</v>
+        <v>830947242.5855429</v>
       </c>
       <c r="F38">
-        <v>291052296</v>
+        <v>-259025429</v>
       </c>
       <c r="G38">
-        <v>1276625429.349087</v>
+        <v>287268665.64956015</v>
+      </c>
+      <c r="H38">
+        <v>320280361.8332608</v>
+      </c>
+      <c r="I38">
+        <v>1404826761.5709429</v>
       </c>
     </row>
     <row r="39"/>
@@ -1984,22 +2230,28 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>8001050</v>
+        <v>41743522</v>
       </c>
       <c r="C40">
-        <v>-38878243</v>
+        <v>8804531.777498882</v>
       </c>
       <c r="D40">
-        <v>-222511506.14466646</v>
+        <v>-42782475.54343786</v>
       </c>
       <c r="E40">
-        <v>-57184271</v>
+        <v>-244856565.91445544</v>
       </c>
       <c r="F40">
-        <v>-55596370</v>
+        <v>-70390669</v>
       </c>
       <c r="G40">
-        <v>453503314.2605063</v>
+        <v>-62926832.25234286</v>
+      </c>
+      <c r="H40">
+        <v>-61179470.99175553</v>
+      </c>
+      <c r="I40">
+        <v>499045043.0390623</v>
       </c>
     </row>
     <row r="41">
@@ -2012,22 +2264,28 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>8001050</v>
+        <v>41743522</v>
       </c>
       <c r="C42">
-        <v>-38878243</v>
+        <v>8804531.777498882</v>
       </c>
       <c r="D42">
-        <v>-222511506.14466646</v>
+        <v>-42782475.54343786</v>
       </c>
       <c r="E42">
-        <v>-57184271</v>
+        <v>-244856565.91445544</v>
       </c>
       <c r="F42">
-        <v>-55596370</v>
+        <v>-70390669</v>
       </c>
       <c r="G42">
-        <v>453503314.2605063</v>
+        <v>-62926832.25234286</v>
+      </c>
+      <c r="H42">
+        <v>-61179470.99175553</v>
+      </c>
+      <c r="I42">
+        <v>499045043.0390623</v>
       </c>
     </row>
     <row r="43">
@@ -2035,22 +2293,28 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-780037326</v>
+        <v>-160816512</v>
       </c>
       <c r="C43">
-        <v>-740900402</v>
+        <v>-858370266.9527444</v>
       </c>
       <c r="D43">
-        <v>532605359.0451476</v>
+        <v>-815303133.1351131</v>
       </c>
       <c r="E43">
-        <v>203868902</v>
+        <v>586090676.6710874</v>
       </c>
       <c r="F43">
-        <v>235455926</v>
+        <v>-329416098</v>
       </c>
       <c r="G43">
-        <v>1730128743.6095934</v>
+        <v>224341833.3972173</v>
+      </c>
+      <c r="H43">
+        <v>259100890.84150523</v>
+      </c>
+      <c r="I43">
+        <v>1903871804.6100051</v>
       </c>
     </row>
     <row r="44">
@@ -2064,22 +2328,28 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-780037326</v>
+        <v>-160816512</v>
       </c>
       <c r="C46">
-        <v>-740900402</v>
+        <v>-858370266.9527444</v>
       </c>
       <c r="D46">
-        <v>532605359.0451476</v>
+        <v>-815303133.1351131</v>
       </c>
       <c r="E46">
-        <v>203868902</v>
+        <v>586090676.6710874</v>
       </c>
       <c r="F46">
-        <v>235455926</v>
+        <v>-329416098</v>
       </c>
       <c r="G46">
-        <v>1730128743.6095934</v>
+        <v>224341833.3972173</v>
+      </c>
+      <c r="H46">
+        <v>259100890.84150523</v>
+      </c>
+      <c r="I46">
+        <v>1903871804.6100051</v>
       </c>
     </row>
     <row r="47">
@@ -2098,10 +2368,13 @@
       <c r="E47">
         <v>0</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>0</v>
       </c>
-      <c r="G47">
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
         <v>0</v>
       </c>
     </row>
@@ -2110,22 +2383,28 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-780037326</v>
+        <v>-160816512</v>
       </c>
       <c r="C48">
-        <v>-740900402</v>
+        <v>-858370266.9527444</v>
       </c>
       <c r="D48">
-        <v>532605359.0451476</v>
+        <v>-815303133.1351131</v>
       </c>
       <c r="E48">
-        <v>203868902</v>
+        <v>586090676.6710874</v>
       </c>
       <c r="F48">
-        <v>235455926</v>
+        <v>-329416098</v>
       </c>
       <c r="G48">
-        <v>1730128743.6095934</v>
+        <v>224341833.3972173</v>
+      </c>
+      <c r="H48">
+        <v>259100890.84150523</v>
+      </c>
+      <c r="I48">
+        <v>1903871804.6100051</v>
       </c>
     </row>
     <row r="49"/>
@@ -2134,34 +2413,40 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>79129948</v>
+        <v>107977680</v>
       </c>
       <c r="C50">
-        <v>46685219.508110546</v>
+        <v>87076338.9452427</v>
       </c>
       <c r="D50">
-        <v>145587457.87009963</v>
+        <v>51373444.57273359</v>
       </c>
       <c r="E50">
-        <v>74260929</v>
+        <v>160207647.64906758</v>
       </c>
       <c r="F50">
-        <v>44013541.04487084</v>
+        <v>61774556</v>
       </c>
       <c r="G50">
-        <v>142093231.71564442</v>
+        <v>81718363.1157271</v>
+      </c>
+      <c r="H50">
+        <v>48433470.70319729</v>
+      </c>
+      <c r="I50">
+        <v>156362524.16969067</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:I50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2170,6 +2455,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2177,21 +2464,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -2205,16 +2498,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>4957758924</v>
+        <v>7580928092.255226</v>
       </c>
       <c r="C3">
-        <v>2032002479</v>
+        <v>5455627197.872362</v>
+      </c>
+      <c r="D3">
+        <v>2236060316.8724113</v>
       </c>
       <c r="E3">
-        <v>4817420653</v>
+        <v>7539675442.485939</v>
       </c>
       <c r="F3">
-        <v>3717653550</v>
+        <v>4540635582.668243</v>
+      </c>
+      <c r="G3">
+        <v>5301195871.156651</v>
+      </c>
+      <c r="H3">
+        <v>4090987910.175106</v>
       </c>
     </row>
     <row r="4">
@@ -2226,28 +2528,28 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
-      <c r="B5">
-        <v>3721518120</v>
-      </c>
       <c r="C5">
-        <v>699352685</v>
-      </c>
-      <c r="F5">
-        <v>1196473153</v>
+        <v>4095240568.1851635</v>
+      </c>
+      <c r="D5">
+        <v>769583109.5620782</v>
+      </c>
+      <c r="H5">
+        <v>1316625429.9764135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
-      <c r="B6">
-        <v>1384901206</v>
-      </c>
       <c r="C6">
-        <v>1342320390</v>
-      </c>
-      <c r="F6">
-        <v>2387580968</v>
+        <v>1523975812.7900121</v>
+      </c>
+      <c r="D6">
+        <v>1477118944.3060215</v>
+      </c>
+      <c r="H6">
+        <v>2627346723.75595</v>
       </c>
     </row>
     <row r="7">
@@ -2255,16 +2557,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-4112360264</v>
+        <v>-6350916488.449118</v>
       </c>
       <c r="C7">
-        <v>-2011008287</v>
+        <v>-4525331878.304934</v>
+      </c>
+      <c r="D7">
+        <v>-2212957845.2459483</v>
       </c>
       <c r="E7">
-        <v>-4169723957</v>
+        <v>-5609363241.204662</v>
       </c>
       <c r="F7">
-        <v>-3078611482</v>
+        <v>-4565446815.605094</v>
+      </c>
+      <c r="G7">
+        <v>-4588456150.48086</v>
+      </c>
+      <c r="H7">
+        <v>-3387771932.9140463</v>
       </c>
     </row>
     <row r="8">
@@ -2272,22 +2583,34 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>845398660</v>
+        <v>1230011603.8061085</v>
       </c>
       <c r="C8">
-        <v>20994192</v>
+        <v>930295319.5674285</v>
+      </c>
+      <c r="D8">
+        <v>23102471.62646313</v>
       </c>
       <c r="E8">
-        <v>647696696</v>
+        <v>1930312201.2812743</v>
       </c>
       <c r="F8">
-        <v>639042068</v>
+        <v>-24811232.93685031</v>
+      </c>
+      <c r="G8">
+        <v>712739720.6757905</v>
+      </c>
+      <c r="H8">
+        <v>703215977.2610598</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
       </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -2298,6 +2621,9 @@
       <c r="A11" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -2309,16 +2635,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>845398660</v>
+        <v>1230011603.8061085</v>
       </c>
       <c r="C13">
-        <v>20994192</v>
+        <v>930295319.5674285</v>
+      </c>
+      <c r="D13">
+        <v>23102471.62646313</v>
       </c>
       <c r="E13">
-        <v>647696696</v>
+        <v>1930312201.2812743</v>
       </c>
       <c r="F13">
-        <v>639042068</v>
+        <v>-24811232.93685031</v>
+      </c>
+      <c r="G13">
+        <v>712739720.6757905</v>
+      </c>
+      <c r="H13">
+        <v>703215977.2610598</v>
       </c>
     </row>
     <row r="14"/>
@@ -2327,16 +2662,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-192224761</v>
+        <v>-129313557.91841471</v>
       </c>
       <c r="C15">
-        <v>-197167910</v>
+        <v>-211528363.98305574</v>
+      </c>
+      <c r="D15">
+        <v>-216967914.09852955</v>
       </c>
       <c r="E15">
-        <v>-145559002</v>
+        <v>-278214444.6408465</v>
       </c>
       <c r="F15">
-        <v>-173761460</v>
+        <v>-112583045.21923691</v>
+      </c>
+      <c r="G15">
+        <v>-160176334.1823915</v>
+      </c>
+      <c r="H15">
+        <v>-191210940.5983716</v>
       </c>
     </row>
     <row r="16">
@@ -2344,16 +2688,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-92524572</v>
+        <v>-46186115.501632094</v>
       </c>
       <c r="C16">
-        <v>-66307087</v>
+        <v>-101816078.43639065</v>
+      </c>
+      <c r="D16">
+        <v>-72965780.06197725</v>
       </c>
       <c r="E16">
-        <v>-100987204</v>
+        <v>-75113007.23300141</v>
       </c>
       <c r="F16">
-        <v>-79734000</v>
+        <v>-88459986.69878227</v>
+      </c>
+      <c r="G16">
+        <v>-111128545.22078505</v>
+      </c>
+      <c r="H16">
+        <v>-87741051.08043268</v>
       </c>
     </row>
     <row r="17">
@@ -2366,16 +2719,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>291172224</v>
+        <v>109311741.30260086</v>
       </c>
       <c r="C18">
-        <v>118824605</v>
+        <v>320412333.24788904</v>
+      </c>
+      <c r="D18">
+        <v>130757214.44951008</v>
       </c>
       <c r="E18">
-        <v>244308866</v>
+        <v>139713780.83162147</v>
       </c>
       <c r="F18">
-        <v>147860827</v>
+        <v>-147670308.30093318</v>
+      </c>
+      <c r="G18">
+        <v>268842861.15218836</v>
+      </c>
+      <c r="H18">
+        <v>162709313.14874482</v>
       </c>
     </row>
     <row r="19">
@@ -2383,16 +2745,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-211905807</v>
+        <v>-92469929.3569113</v>
       </c>
       <c r="C19">
-        <v>-140895610</v>
+        <v>-233185820.80702475</v>
+      </c>
+      <c r="D19">
+        <v>-155044634.83606395</v>
       </c>
       <c r="E19">
-        <v>-34685949</v>
+        <v>-78934248.35567355</v>
       </c>
       <c r="F19">
-        <v>-104919137</v>
+        <v>-38206801.2190007</v>
+      </c>
+      <c r="G19">
+        <v>-38169182.82015556</v>
+      </c>
+      <c r="H19">
+        <v>-115455330.96084374</v>
       </c>
     </row>
     <row r="20">
@@ -2405,16 +2776,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>639915744</v>
+        <v>1071353742.3317511</v>
       </c>
       <c r="C21">
-        <v>-264551810</v>
+        <v>704177389.5888464</v>
+      </c>
+      <c r="D21">
+        <v>-291118642.9205975</v>
       </c>
       <c r="E21">
-        <v>610773407</v>
+        <v>1637764281.8833747</v>
       </c>
       <c r="F21">
-        <v>428488298</v>
+        <v>-411731374.3748033</v>
+      </c>
+      <c r="G21">
+        <v>672108519.6046467</v>
+      </c>
+      <c r="H21">
+        <v>471517967.77015656</v>
       </c>
     </row>
     <row r="22"/>
@@ -2433,16 +2813,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>1143579</v>
+        <v>34625298.72065842</v>
       </c>
       <c r="C25">
-        <v>12644343</v>
+        <v>1258419.5381331686</v>
+      </c>
+      <c r="D25">
+        <v>13914113.741208412</v>
       </c>
       <c r="E25">
-        <v>1293021</v>
+        <v>57374114.370758936</v>
       </c>
       <c r="F25">
-        <v>1185094</v>
+        <v>30290417.63189873</v>
+      </c>
+      <c r="G25">
+        <v>1422868.8089030043</v>
+      </c>
+      <c r="H25">
+        <v>1304103.5591982629</v>
       </c>
     </row>
     <row r="26">
@@ -2450,16 +2839,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-93608</v>
+        <v>-81605.55784647696</v>
       </c>
       <c r="C26">
-        <v>-98416</v>
+        <v>-103008.30648828784</v>
+      </c>
+      <c r="D26">
+        <v>-108299.1356652352</v>
       </c>
       <c r="E26">
-        <v>-69236</v>
+        <v>4063.8941181353584</v>
       </c>
       <c r="F26">
-        <v>-63456</v>
+        <v>9301.201569779194</v>
+      </c>
+      <c r="G26">
+        <v>-76188.82048567534</v>
+      </c>
+      <c r="H26">
+        <v>-69828.38108410385</v>
       </c>
     </row>
     <row r="27">
@@ -2497,16 +2895,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>640965715</v>
+        <v>1105897435.494563</v>
       </c>
       <c r="C33">
-        <v>-252005883</v>
+        <v>705332800.8204913</v>
+      </c>
+      <c r="D33">
+        <v>-277312828.31505436</v>
       </c>
       <c r="E33">
-        <v>611997192</v>
+        <v>1695142460.1482515</v>
       </c>
       <c r="F33">
-        <v>429609936</v>
+        <v>-381431655.54133487</v>
+      </c>
+      <c r="G33">
+        <v>673455199.5930641</v>
+      </c>
+      <c r="H33">
+        <v>472752242.94827074</v>
       </c>
     </row>
     <row r="34"/>
@@ -2515,16 +2922,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>56530735</v>
+        <v>105645467.43596092</v>
       </c>
       <c r="C35">
-        <v>66106560</v>
+        <v>62207666.83283673</v>
+      </c>
+      <c r="D35">
+        <v>72745115.73120235</v>
       </c>
       <c r="E35">
-        <v>19686678</v>
+        <v>34505347.193680406</v>
       </c>
       <c r="F35">
-        <v>18043447</v>
+        <v>374789337.810343</v>
+      </c>
+      <c r="G35">
+        <v>21663654.4009084</v>
+      </c>
+      <c r="H35">
+        <v>19855406.78874859</v>
       </c>
     </row>
     <row r="36">
@@ -2532,16 +2948,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-944777764</v>
+        <v>-947293273.2969718</v>
       </c>
       <c r="C36">
-        <v>-851429657</v>
+        <v>-1039654276.102804</v>
+      </c>
+      <c r="D36">
+        <v>-936931961.6002243</v>
       </c>
       <c r="E36">
-        <v>-370872371</v>
+        <v>-1298173208.3060145</v>
       </c>
       <c r="F36">
-        <v>-703634332</v>
+        <v>-938399400.9629982</v>
+      </c>
+      <c r="G36">
+        <v>-408116131.7409408</v>
+      </c>
+      <c r="H36">
+        <v>-774294728.296061</v>
       </c>
     </row>
     <row r="37">
@@ -2549,16 +2974,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>161265097</v>
+        <v>400365135.09669113</v>
       </c>
       <c r="C37">
-        <v>335306821</v>
+        <v>177459667.3109079</v>
+      </c>
+      <c r="D37">
+        <v>368979016.59240097</v>
       </c>
       <c r="E37">
-        <v>-290810622</v>
+        <v>658498072.5496254</v>
       </c>
       <c r="F37">
-        <v>547033245</v>
+        <v>398747624.04442966</v>
+      </c>
+      <c r="G37">
+        <v>-320014418.4367322</v>
+      </c>
+      <c r="H37">
+        <v>601967440.3923025</v>
       </c>
     </row>
     <row r="38">
@@ -2566,16 +3000,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>-86016217</v>
+        <v>664614764.7302433</v>
       </c>
       <c r="C38">
-        <v>-702022159</v>
+        <v>-94654141.13856804</v>
+      </c>
+      <c r="D38">
+        <v>-772520657.5916753</v>
       </c>
       <c r="E38">
-        <v>-29999123</v>
+        <v>1089972671.585543</v>
       </c>
       <c r="F38">
-        <v>291052296</v>
+        <v>-546294094.6495602</v>
+      </c>
+      <c r="G38">
+        <v>-33011696.18370062</v>
+      </c>
+      <c r="H38">
+        <v>320280361.8332608</v>
       </c>
     </row>
     <row r="39"/>
@@ -2584,16 +3027,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>46879293</v>
+        <v>32938990.222501118</v>
       </c>
       <c r="C40">
-        <v>-38878243</v>
+        <v>51587007.32093674</v>
+      </c>
+      <c r="D40">
+        <v>-42782475.54343786</v>
       </c>
       <c r="E40">
-        <v>-1587901</v>
+        <v>-174465896.91445544</v>
       </c>
       <c r="F40">
-        <v>-55596370</v>
+        <v>-7463836.747657143</v>
+      </c>
+      <c r="G40">
+        <v>-1747361.2605873272</v>
+      </c>
+      <c r="H40">
+        <v>-61179470.99175553</v>
       </c>
     </row>
     <row r="41">
@@ -2606,16 +3058,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>46879293</v>
+        <v>32938990.222501118</v>
       </c>
       <c r="C42">
-        <v>-38878243</v>
+        <v>51587007.32093674</v>
+      </c>
+      <c r="D42">
+        <v>-42782475.54343786</v>
       </c>
       <c r="E42">
-        <v>-1587901</v>
+        <v>-174465896.91445544</v>
       </c>
       <c r="F42">
-        <v>-55596370</v>
+        <v>-7463836.747657143</v>
+      </c>
+      <c r="G42">
+        <v>-1747361.2605873272</v>
+      </c>
+      <c r="H42">
+        <v>-61179470.99175553</v>
       </c>
     </row>
     <row r="43">
@@ -2623,16 +3084,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-39136924</v>
+        <v>697553754.9527444</v>
       </c>
       <c r="C43">
-        <v>-740900402</v>
+        <v>-43067133.817631245</v>
+      </c>
+      <c r="D43">
+        <v>-815303133.1351131</v>
       </c>
       <c r="E43">
-        <v>-31587024</v>
+        <v>915506774.6710874</v>
       </c>
       <c r="F43">
-        <v>235455926</v>
+        <v>-553757931.3972173</v>
+      </c>
+      <c r="G43">
+        <v>-34759057.444287926</v>
+      </c>
+      <c r="H43">
+        <v>259100890.84150523</v>
       </c>
     </row>
     <row r="44">
@@ -2646,16 +3116,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-39136924</v>
+        <v>697553754.9527444</v>
       </c>
       <c r="C46">
-        <v>-740900402</v>
+        <v>-43067133.817631245</v>
+      </c>
+      <c r="D46">
+        <v>-815303133.1351131</v>
       </c>
       <c r="E46">
-        <v>-31587024</v>
+        <v>915506774.6710874</v>
       </c>
       <c r="F46">
-        <v>235455926</v>
+        <v>-553757931.3972173</v>
+      </c>
+      <c r="G46">
+        <v>-34759057.444287926</v>
+      </c>
+      <c r="H46">
+        <v>259100890.84150523</v>
       </c>
     </row>
     <row r="47">
@@ -2668,10 +3147,13 @@
       <c r="C47">
         <v>0</v>
       </c>
-      <c r="E47">
+      <c r="D47">
         <v>0</v>
       </c>
-      <c r="F47">
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
         <v>0</v>
       </c>
     </row>
@@ -2680,16 +3162,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-39136924</v>
+        <v>697553754.9527444</v>
       </c>
       <c r="C48">
-        <v>-740900402</v>
+        <v>-43067133.817631245</v>
+      </c>
+      <c r="D48">
+        <v>-815303133.1351131</v>
       </c>
       <c r="E48">
-        <v>-31587024</v>
+        <v>915506774.6710874</v>
       </c>
       <c r="F48">
-        <v>235455926</v>
+        <v>-553757931.3972173</v>
+      </c>
+      <c r="G48">
+        <v>-34759057.444287926</v>
+      </c>
+      <c r="H48">
+        <v>259100890.84150523</v>
       </c>
     </row>
     <row r="49"/>
@@ -2698,28 +3189,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>32444728.491889454</v>
+        <v>20901341.054757297</v>
       </c>
       <c r="C50">
-        <v>46685219.508110546</v>
+        <v>35702894.372509114</v>
+      </c>
+      <c r="D50">
+        <v>51373444.57273359</v>
       </c>
       <c r="E50">
-        <v>30247387.95512916</v>
+        <v>98433091.64906758</v>
       </c>
       <c r="F50">
-        <v>44013541.04487084</v>
+        <v>-19943807.115727097</v>
+      </c>
+      <c r="G50">
+        <v>33284892.412529804</v>
+      </c>
+      <c r="H50">
+        <v>48433470.70319729</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:I50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2728,6 +3228,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2735,21 +3237,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -2763,16 +3271,19 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>17967650400.439323</v>
+        <v>22812291049.48594</v>
       </c>
       <c r="C3">
-        <v>17827312129.439323</v>
+        <v>19771998539.898956</v>
       </c>
       <c r="D3">
-        <v>19512963200.439323</v>
-      </c>
-      <c r="G3">
-        <v>22739160575.93671</v>
+        <v>19617567213.183243</v>
+      </c>
+      <c r="E3">
+        <v>21472494806.48594</v>
+      </c>
+      <c r="I3">
+        <v>25022673509.662426</v>
       </c>
     </row>
     <row r="4">
@@ -2795,16 +3306,19 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-15369648314.915365</v>
+        <v>-18698569453.204662</v>
       </c>
       <c r="C7">
-        <v>-15427012007.915365</v>
+        <v>-16913099780.36064</v>
       </c>
       <c r="D7">
-        <v>-16494615202.915365</v>
-      </c>
-      <c r="G7">
-        <v>-19525873398.24762</v>
+        <v>-16976224052.536564</v>
+      </c>
+      <c r="E7">
+        <v>-18151038140.204662</v>
+      </c>
+      <c r="I7">
+        <v>-21486701472.718113</v>
       </c>
     </row>
     <row r="8">
@@ -2812,16 +3326,19 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>2598002085.523956</v>
+        <v>4113721596.2812743</v>
       </c>
       <c r="C8">
-        <v>2400300121.523956</v>
+        <v>2858898759.538316</v>
       </c>
       <c r="D8">
-        <v>3018347997.523956</v>
-      </c>
-      <c r="G8">
-        <v>3213287177.689088</v>
+        <v>2641343160.6466775</v>
+      </c>
+      <c r="E8">
+        <v>3321456666.2812743</v>
+      </c>
+      <c r="I8">
+        <v>3535972036.94431</v>
       </c>
     </row>
     <row r="9">
@@ -2849,16 +3366,19 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>2598002085.523956</v>
+        <v>4113721596.2812743</v>
       </c>
       <c r="C13">
-        <v>2400300121.523956</v>
+        <v>2858898759.538316</v>
       </c>
       <c r="D13">
-        <v>3018347997.523956</v>
-      </c>
-      <c r="G13">
-        <v>3213287177.689088</v>
+        <v>2641343160.6466775</v>
+      </c>
+      <c r="E13">
+        <v>3321456666.2812743</v>
+      </c>
+      <c r="I13">
+        <v>3535972036.94431</v>
       </c>
     </row>
     <row r="14"/>
@@ -2867,16 +3387,19 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-744526860.4450238</v>
+        <v>-836024280.6408465</v>
       </c>
       <c r="C15">
-        <v>-697861101.4450238</v>
+        <v>-819293767.9416687</v>
       </c>
       <c r="D15">
-        <v>-674454651.4450238</v>
-      </c>
-      <c r="G15">
-        <v>-574117904.6768087</v>
+        <v>-767941738.1410044</v>
+      </c>
+      <c r="E15">
+        <v>-742184764.6408465</v>
+      </c>
+      <c r="I15">
+        <v>-631771996.8951621</v>
       </c>
     </row>
     <row r="16">
@@ -2884,16 +3407,19 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-307477349.21632606</v>
+        <v>-296080981.2330014</v>
       </c>
       <c r="C16">
-        <v>-315939981.21632606</v>
+        <v>-338354852.4301516</v>
       </c>
       <c r="D16">
-        <v>-329366894.21632606</v>
-      </c>
-      <c r="G16">
-        <v>-389867197.7795394</v>
+        <v>-347667319.21454597</v>
+      </c>
+      <c r="E16">
+        <v>-362442590.2330014</v>
+      </c>
+      <c r="I16">
+        <v>-429018457.80921215</v>
       </c>
     </row>
     <row r="17">
@@ -2906,16 +3432,19 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>402766396.3413288</v>
+        <v>700195069.8316214</v>
       </c>
       <c r="C18">
-        <v>355903038.3413288</v>
+        <v>443213020.2280874</v>
       </c>
       <c r="D18">
-        <v>384939260.3413288</v>
-      </c>
-      <c r="G18">
-        <v>1322675710.0327792</v>
+        <v>391643548.13238674</v>
+      </c>
+      <c r="E18">
+        <v>423595646.83162147</v>
+      </c>
+      <c r="I18">
+        <v>1455501505.4660954</v>
       </c>
     </row>
     <row r="19">
@@ -2923,16 +3452,19 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-459252437.72261405</v>
+        <v>-559634633.3556736</v>
       </c>
       <c r="C19">
-        <v>-282032579.72261405</v>
+        <v>-505371505.21776295</v>
       </c>
       <c r="D19">
-        <v>-246056106.72261402</v>
-      </c>
-      <c r="G19">
-        <v>-1343130868.8358486</v>
+        <v>-310354867.23089373</v>
+      </c>
+      <c r="E19">
+        <v>-270765563.35567355</v>
+      </c>
+      <c r="I19">
+        <v>-1478010813.081397</v>
       </c>
     </row>
     <row r="20">
@@ -2945,16 +3477,19 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>1489511834.4813213</v>
+        <v>3122176770.8833747</v>
       </c>
       <c r="C21">
-        <v>1460369497.4813213</v>
+        <v>1639091654.1768203</v>
       </c>
       <c r="D21">
-        <v>2153409605.4813213</v>
-      </c>
-      <c r="G21">
-        <v>2228846916.4296703</v>
+        <v>1607022784.1926205</v>
+      </c>
+      <c r="E21">
+        <v>2369659394.8833747</v>
+      </c>
+      <c r="I21">
+        <v>2452672274.6246343</v>
       </c>
     </row>
     <row r="22"/>
@@ -2973,16 +3508,19 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>93452385.88124847</v>
+        <v>107171946.37075894</v>
       </c>
       <c r="C25">
-        <v>93601827.88124847</v>
+        <v>102837065.28199925</v>
       </c>
       <c r="D25">
-        <v>82142578.88124847</v>
-      </c>
-      <c r="G25">
-        <v>12620282.245922156</v>
+        <v>103001514.5527691</v>
+      </c>
+      <c r="E25">
+        <v>90391504.37075894</v>
+      </c>
+      <c r="I25">
+        <v>13887636.757078957</v>
       </c>
     </row>
     <row r="26">
@@ -2990,15 +3528,18 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-179878.5728999384</v>
+        <v>-288849.10588186467</v>
       </c>
       <c r="C26">
-        <v>-155506.5728999384</v>
+        <v>-197942.34646560848</v>
       </c>
       <c r="D26">
-        <v>-120546.57289993837</v>
-      </c>
-      <c r="G26">
+        <v>-171122.860462996</v>
+      </c>
+      <c r="E26">
+        <v>-132652.10588186464</v>
+      </c>
+      <c r="I26">
         <v>0</v>
       </c>
     </row>
@@ -3037,16 +3578,19 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>1582784341.7896695</v>
+        <v>3229059868.1482515</v>
       </c>
       <c r="C33">
-        <v>1553815818.7896695</v>
+        <v>1741730777.1123538</v>
       </c>
       <c r="D33">
-        <v>2235431637.7896695</v>
-      </c>
-      <c r="G33">
-        <v>2241467198.6755924</v>
+        <v>1709853175.8849263</v>
+      </c>
+      <c r="E33">
+        <v>2459918247.1482515</v>
+      </c>
+      <c r="I33">
+        <v>2466559911.381713</v>
       </c>
     </row>
     <row r="34"/>
@@ -3055,16 +3599,19 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>494580667.1416717</v>
+        <v>275103597.1936804</v>
       </c>
       <c r="C35">
-        <v>457736610.1416717</v>
+        <v>544247467.5680625</v>
       </c>
       <c r="D35">
-        <v>409673497.1416717</v>
-      </c>
-      <c r="G35">
-        <v>172748437.68521506</v>
+        <v>503703455.1361342</v>
+      </c>
+      <c r="E35">
+        <v>450813746.1936804</v>
+      </c>
+      <c r="I35">
+        <v>190096188.51435268</v>
       </c>
     </row>
     <row r="36">
@@ -3072,16 +3619,19 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-3828675441.744117</v>
+        <v>-4222052719.3060145</v>
       </c>
       <c r="C36">
-        <v>-3254770048.744117</v>
+        <v>-4213158846.9720407</v>
       </c>
       <c r="D36">
-        <v>-3106974723.744117</v>
-      </c>
-      <c r="G36">
-        <v>-2612395123.258974</v>
+        <v>-3581620702.610178</v>
+      </c>
+      <c r="E36">
+        <v>-3418983469.3060145</v>
+      </c>
+      <c r="I36">
+        <v>-2874737175.510308</v>
       </c>
     </row>
     <row r="37">
@@ -3089,16 +3639,19 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>1457335749.0025892</v>
+        <v>1605301891.5496254</v>
       </c>
       <c r="C37">
-        <v>1005260030.0025892</v>
+        <v>1603684380.497364</v>
       </c>
       <c r="D37">
-        <v>1216986454.0025892</v>
-      </c>
-      <c r="G37">
-        <v>1474804916.2472537</v>
+        <v>1106210294.749724</v>
+      </c>
+      <c r="E37">
+        <v>1339198718.5496254</v>
+      </c>
+      <c r="I37">
+        <v>1622907837.185185</v>
       </c>
     </row>
     <row r="38">
@@ -3106,16 +3659,19 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>-293974683.8101859</v>
+        <v>887412637.5855429</v>
       </c>
       <c r="C38">
-        <v>-237957589.8101859</v>
+        <v>-323496221.7942606</v>
       </c>
       <c r="D38">
-        <v>755116865.1898141</v>
-      </c>
-      <c r="G38">
-        <v>1276625429.349087</v>
+        <v>-261853776.83939314</v>
+      </c>
+      <c r="E38">
+        <v>830947242.5855429</v>
+      </c>
+      <c r="I38">
+        <v>1404826761.5709429</v>
       </c>
     </row>
     <row r="39"/>
@@ -3124,16 +3680,19 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-157326185.14466646</v>
+        <v>-132722374.91445544</v>
       </c>
       <c r="C40">
-        <v>-205793379.14466646</v>
+        <v>-173125201.88461372</v>
       </c>
       <c r="D40">
-        <v>-222511506.14466646</v>
-      </c>
-      <c r="G40">
-        <v>453503314.2605063</v>
+        <v>-226459570.4661378</v>
+      </c>
+      <c r="E40">
+        <v>-244856565.91445544</v>
+      </c>
+      <c r="I40">
+        <v>499045043.0390623</v>
       </c>
     </row>
     <row r="41">
@@ -3146,16 +3705,19 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-157326185.14466646</v>
+        <v>-132722374.91445544</v>
       </c>
       <c r="C42">
-        <v>-205793379.14466646</v>
+        <v>-173125201.88461372</v>
       </c>
       <c r="D42">
-        <v>-222511506.14466646</v>
-      </c>
-      <c r="G42">
-        <v>453503314.2605063</v>
+        <v>-226459570.4661378</v>
+      </c>
+      <c r="E42">
+        <v>-244856565.91445544</v>
+      </c>
+      <c r="I42">
+        <v>499045043.0390623</v>
       </c>
     </row>
     <row r="43">
@@ -3163,16 +3725,19 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>-451300868.9548524</v>
+        <v>754690262.6710874</v>
       </c>
       <c r="C43">
-        <v>-443750968.9548524</v>
+        <v>-496621423.67887425</v>
       </c>
       <c r="D43">
-        <v>532605359.0451476</v>
-      </c>
-      <c r="G43">
-        <v>1730128743.6095934</v>
+        <v>-488313347.30553097</v>
+      </c>
+      <c r="E43">
+        <v>586090676.6710874</v>
+      </c>
+      <c r="I43">
+        <v>1903871804.6100051</v>
       </c>
     </row>
     <row r="44">
@@ -3186,32 +3751,35 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>-451300868.9548524</v>
+        <v>754690262.6710874</v>
       </c>
       <c r="C46">
-        <v>-443750968.9548524</v>
+        <v>-496621423.67887425</v>
       </c>
       <c r="D46">
-        <v>532605359.0451476</v>
-      </c>
-      <c r="G46">
-        <v>1730128743.6095934</v>
+        <v>-488313347.30553097</v>
+      </c>
+      <c r="E46">
+        <v>586090676.6710874</v>
+      </c>
+      <c r="I46">
+        <v>1903871804.6100051</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
-      <c r="G47">
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="I47">
         <v>0</v>
       </c>
     </row>
@@ -3220,16 +3788,19 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>-451300868.9548524</v>
+        <v>754690262.6710874</v>
       </c>
       <c r="C48">
-        <v>-443750968.9548524</v>
+        <v>-496621423.67887425</v>
       </c>
       <c r="D48">
-        <v>532605359.0451476</v>
-      </c>
-      <c r="G48">
-        <v>1730128743.6095934</v>
+        <v>-488313347.30553097</v>
+      </c>
+      <c r="E48">
+        <v>586090676.6710874</v>
+      </c>
+      <c r="I48">
+        <v>1903871804.6100051</v>
       </c>
     </row>
     <row r="49"/>
@@ -3238,28 +3809,31 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>150456476.87009963</v>
+        <v>206410771.64906758</v>
       </c>
       <c r="C50">
-        <v>148259136.33333933</v>
+        <v>165565623.4785832</v>
       </c>
       <c r="D50">
-        <v>145587457.87009963</v>
-      </c>
-      <c r="G50">
-        <v>142093231.71564442</v>
+        <v>163147621.51860386</v>
+      </c>
+      <c r="E50">
+        <v>160207647.64906758</v>
+      </c>
+      <c r="I50">
+        <v>156362524.16969067</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:I129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3268,6 +3842,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3275,21 +3851,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -3303,22 +3885,28 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-3230013340</v>
+        <v>-2068980830</v>
       </c>
       <c r="C3">
-        <v>-2250963147.920317</v>
+        <v>-3554377874.6258683</v>
       </c>
       <c r="D3">
-        <v>-5468721238.052443</v>
+        <v>-2477009463.238369</v>
       </c>
       <c r="E3">
-        <v>-3493602214</v>
+        <v>-6017901390.78193</v>
       </c>
       <c r="F3">
-        <v>-1791204095.389241</v>
+        <v>-3549456403</v>
       </c>
       <c r="G3">
-        <v>736837809.1897215</v>
+        <v>-3844436881.5472283</v>
+      </c>
+      <c r="H3">
+        <v>-1971080467.9186747</v>
+      </c>
+      <c r="I3">
+        <v>810832566.4598473</v>
       </c>
     </row>
     <row r="4">
@@ -3326,22 +3914,28 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-780037326</v>
+        <v>-160816512</v>
       </c>
       <c r="C4">
-        <v>-740900402.6082169</v>
+        <v>-858370266.9527444</v>
       </c>
       <c r="D4">
-        <v>532605359.0451476</v>
+        <v>-815303133.8044084</v>
       </c>
       <c r="E4">
-        <v>203868902</v>
+        <v>586090676.6710874</v>
       </c>
       <c r="F4">
-        <v>304572871.52626497</v>
+        <v>-329416098</v>
       </c>
       <c r="G4">
-        <v>1730128743.6095934</v>
+        <v>224341833.3972173</v>
+      </c>
+      <c r="H4">
+        <v>335158701.1601083</v>
+      </c>
+      <c r="I4">
+        <v>1903871804.6100051</v>
       </c>
     </row>
     <row r="5">
@@ -3349,22 +3943,28 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>-91856861</v>
+        <v>154069450</v>
       </c>
       <c r="C5">
-        <v>134451832.00034153</v>
+        <v>-101081314.53444208</v>
       </c>
       <c r="D5">
-        <v>519752921.54705524</v>
+        <v>147953759.4928101</v>
       </c>
       <c r="E5">
-        <v>-665454</v>
+        <v>571947571.157402</v>
       </c>
       <c r="F5">
-        <v>582033283.0627342</v>
+        <v>1912788169</v>
       </c>
       <c r="G5">
-        <v>-32917764.130232394</v>
+        <v>-732280.249400234</v>
+      </c>
+      <c r="H5">
+        <v>640482253.7401774</v>
+      </c>
+      <c r="I5">
+        <v>-36223433.21549597</v>
       </c>
     </row>
     <row r="6">
@@ -3372,22 +3972,28 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>79129948</v>
+        <v>107977680</v>
       </c>
       <c r="C6">
-        <v>46685219.508110546</v>
+        <v>87076338.9452427</v>
       </c>
       <c r="D6">
-        <v>145587457.87009963</v>
+        <v>51373444.57273359</v>
       </c>
       <c r="E6">
-        <v>74260929</v>
+        <v>160207647.64906758</v>
       </c>
       <c r="F6">
-        <v>44013541.04487084</v>
+        <v>61774556</v>
       </c>
       <c r="G6">
-        <v>142093231.71564442</v>
+        <v>81718363.1157271</v>
+      </c>
+      <c r="H6">
+        <v>48433470.70319729</v>
+      </c>
+      <c r="I6">
+        <v>156362524.16969067</v>
       </c>
     </row>
     <row r="7">
@@ -3400,22 +4006,28 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>16668366</v>
+        <v>11025077</v>
       </c>
       <c r="C8">
-        <v>19760578.05188256</v>
+        <v>18342237.347095937</v>
       </c>
       <c r="D8">
-        <v>25012465.901324</v>
+        <v>21744975.64688972</v>
       </c>
       <c r="E8">
-        <v>31103539</v>
+        <v>27524268.797447134</v>
       </c>
       <c r="F8">
-        <v>27394449.721761573</v>
+        <v>-14420782</v>
       </c>
       <c r="G8">
-        <v>14290766.375694806</v>
+        <v>34227019.893410966</v>
+      </c>
+      <c r="H8">
+        <v>30145456.296654213</v>
+      </c>
+      <c r="I8">
+        <v>15725874.313948477</v>
       </c>
     </row>
     <row r="9">
@@ -3478,10 +4090,16 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>-8001050</v>
-      </c>
-      <c r="E20">
-        <v>57184271</v>
+        <v>-41743522</v>
+      </c>
+      <c r="C20">
+        <v>-8804531.777498882</v>
+      </c>
+      <c r="F20">
+        <v>70390669</v>
+      </c>
+      <c r="G20">
+        <v>62926832.25234286</v>
       </c>
     </row>
     <row r="21">
@@ -3494,22 +4112,28 @@
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B22">
-        <v>192024</v>
+        <v>-34457231</v>
       </c>
       <c r="C22">
-        <v>98416.36894233225</v>
+        <v>211307.44215352304</v>
       </c>
       <c r="D22">
-        <v>-2753487.141486573</v>
+        <v>108299.54165750976</v>
       </c>
       <c r="E22">
-        <v>-2345423</v>
+        <v>-3029997.9422892113</v>
       </c>
       <c r="F22">
-        <v>-2646907.663532528</v>
+        <v>-3229275</v>
       </c>
       <c r="G22">
-        <v>-12620282.245922156</v>
+        <v>-2580955.1665314883</v>
+      </c>
+      <c r="H22">
+        <v>-2912715.535545643</v>
+      </c>
+      <c r="I22">
+        <v>-13887636.757078957</v>
       </c>
     </row>
     <row r="23">
@@ -3536,17 +4160,17 @@
       <c r="A27" t="str">
         <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
       </c>
-      <c r="C27">
-        <v>38878243.39135845</v>
-      </c>
       <c r="D27">
-        <v>222511506.14466646</v>
-      </c>
-      <c r="F27">
-        <v>55596369.90989303</v>
-      </c>
-      <c r="G27">
-        <v>-453503314.2605063</v>
+        <v>42782475.97409733</v>
+      </c>
+      <c r="E27">
+        <v>244856565.91445544</v>
+      </c>
+      <c r="H27">
+        <v>61179470.89259983</v>
+      </c>
+      <c r="I27">
+        <v>-499045043.0390623</v>
       </c>
     </row>
     <row r="28">
@@ -3554,22 +4178,28 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-2606251166</v>
+        <v>-2342103350</v>
       </c>
       <c r="C28">
-        <v>-1641114838.5346844</v>
+        <v>-2867976229.51869</v>
       </c>
       <c r="D28">
-        <v>-6508572653.523397</v>
+        <v>-1805918941.4393833</v>
       </c>
       <c r="E28">
-        <v>-3698111530</v>
+        <v>-7162176808.557249</v>
       </c>
       <c r="F28">
-        <v>-2676478075.180339</v>
+        <v>-4399157565</v>
       </c>
       <c r="G28">
-        <v>-951517788.6643221</v>
+        <v>-4069483440.6259193</v>
+      </c>
+      <c r="H28">
+        <v>-2945255468.307827</v>
+      </c>
+      <c r="I28">
+        <v>-1047071147.8056618</v>
       </c>
     </row>
     <row r="29">
@@ -3587,22 +4217,28 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>659014974</v>
+        <v>-3865327419</v>
       </c>
       <c r="C31">
-        <v>2526676715.607023</v>
+        <v>725194603.2621468</v>
       </c>
       <c r="D31">
-        <v>-2615121318.8053393</v>
+        <v>2780410750.342585</v>
       </c>
       <c r="E31">
-        <v>-186367303</v>
+        <v>-2877737141.17977</v>
       </c>
       <c r="F31">
-        <v>-178203507.17479405</v>
+        <v>-1455069747</v>
       </c>
       <c r="G31">
-        <v>-656390342.7272944</v>
+        <v>-205082688.09097093</v>
+      </c>
+      <c r="H31">
+        <v>-196099067.2202054</v>
+      </c>
+      <c r="I31">
+        <v>-722306401.1580788</v>
       </c>
     </row>
     <row r="32">
@@ -3615,22 +4251,28 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1350429513</v>
+        <v>-1413688879</v>
       </c>
       <c r="C33">
-        <v>-555816858.775031</v>
+        <v>-1486042401.9948432</v>
       </c>
       <c r="D33">
-        <v>-392516020.58235663</v>
+        <v>-611633122.5969553</v>
       </c>
       <c r="E33">
-        <v>-649736638</v>
+        <v>-431933280.8062397</v>
       </c>
       <c r="F33">
-        <v>-145645739.3781131</v>
+        <v>-1255644436</v>
       </c>
       <c r="G33">
-        <v>111897842.06165054</v>
+        <v>-714984517.8165727</v>
+      </c>
+      <c r="H33">
+        <v>-160271781.9051146</v>
+      </c>
+      <c r="I33">
+        <v>123134851.83386597</v>
       </c>
     </row>
     <row r="34">
@@ -3653,22 +4295,28 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-6926357257</v>
+        <v>-3062844858</v>
       </c>
       <c r="C37">
-        <v>-7364885042.43107</v>
+        <v>-7621916194.945226</v>
       </c>
       <c r="D37">
-        <v>-3242822012.4658337</v>
+        <v>-8104481835.97285</v>
       </c>
       <c r="E37">
-        <v>-3152910863</v>
+        <v>-3568472820.1333966</v>
       </c>
       <c r="F37">
-        <v>-5043191545.875337</v>
+        <v>-3545194076</v>
       </c>
       <c r="G37">
-        <v>-930356222.1424795</v>
+        <v>-3469532609.4581246</v>
+      </c>
+      <c r="H37">
+        <v>-5549639138.072268</v>
+      </c>
+      <c r="I37">
+        <v>-1023784493.5661284</v>
       </c>
     </row>
     <row r="38">
@@ -3686,22 +4334,28 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>4957707326</v>
+        <v>6061838506</v>
       </c>
       <c r="C40">
-        <v>3746622006.617637</v>
+        <v>5455570418.295851</v>
       </c>
       <c r="D40">
-        <v>-447392671.4781286</v>
+        <v>4122865438.353918</v>
       </c>
       <c r="E40">
-        <v>252912311</v>
+        <v>-492320757.03180224</v>
       </c>
       <c r="F40">
-        <v>2558804312.3832</v>
+        <v>1837214873</v>
       </c>
       <c r="G40">
-        <v>636730897.6581092</v>
+        <v>278310281.6655539</v>
+      </c>
+      <c r="H40">
+        <v>2815764665.9849725</v>
+      </c>
+      <c r="I40">
+        <v>700672714.4745016</v>
       </c>
     </row>
     <row r="41">
@@ -3724,22 +4378,28 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>53813304</v>
+        <v>-62080700</v>
       </c>
       <c r="C44">
-        <v>6288340.446757265</v>
+        <v>59217345.8633814</v>
       </c>
       <c r="D44">
-        <v>189279369.8082607</v>
+        <v>6919828.433918782</v>
       </c>
       <c r="E44">
-        <v>37990963</v>
+        <v>208287190.5939588</v>
       </c>
       <c r="F44">
-        <v>131758404.86470442</v>
+        <v>19535821</v>
       </c>
       <c r="G44">
-        <v>-113399963.51430798</v>
+        <v>41806093.07419455</v>
+      </c>
+      <c r="H44">
+        <v>144989852.90478793</v>
+      </c>
+      <c r="I44">
+        <v>-124787819.3898224</v>
       </c>
     </row>
     <row r="45">
@@ -3767,22 +4427,28 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-3478145353</v>
+        <v>-2348850412</v>
       </c>
       <c r="C49">
-        <v>-2247563409.1425595</v>
+        <v>-3827427811.0058765</v>
       </c>
       <c r="D49">
-        <v>-5456214372.931195</v>
+        <v>-2473268315.7509813</v>
       </c>
       <c r="E49">
-        <v>-3494908082</v>
+        <v>-6004138560.728761</v>
       </c>
       <c r="F49">
-        <v>-1789871920.5913393</v>
+        <v>-2815785494</v>
       </c>
       <c r="G49">
-        <v>745693190.8150387</v>
+        <v>-3845873887.4781027</v>
+      </c>
+      <c r="H49">
+        <v>-1969614513.4075408</v>
+      </c>
+      <c r="I49">
+        <v>820577223.5888473</v>
       </c>
     </row>
     <row r="50">
@@ -3809,6 +4475,12 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>84721493</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -3835,10 +4507,16 @@
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
       <c r="B59">
-        <v>277226357</v>
-      </c>
-      <c r="E59">
-        <v>2559444</v>
+        <v>311260197</v>
+      </c>
+      <c r="C59">
+        <v>305065993.8091563</v>
+      </c>
+      <c r="F59">
+        <v>-817139060</v>
+      </c>
+      <c r="G59">
+        <v>2816468.592338362</v>
       </c>
     </row>
     <row r="60">
@@ -3856,22 +4534,28 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-29094344</v>
+        <v>-31390615</v>
       </c>
       <c r="C62">
-        <v>-3399738.777757319</v>
+        <v>-32016057.429147918</v>
       </c>
       <c r="D62">
-        <v>-12506865.121248208</v>
+        <v>-3741147.487387222</v>
       </c>
       <c r="E62">
-        <v>-1253576</v>
+        <v>-13762830.053170804</v>
       </c>
       <c r="F62">
-        <v>-1332174.797901533</v>
+        <v>-1253342</v>
       </c>
       <c r="G62">
-        <v>-8855381.625317274</v>
+        <v>-1379462.6614644253</v>
+      </c>
+      <c r="H62">
+        <v>-1465954.5111338138</v>
+      </c>
+      <c r="I62">
+        <v>-9744657.129000025</v>
       </c>
     </row>
     <row r="63">
@@ -3895,22 +4579,28 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-982134793</v>
+        <v>-1274377724</v>
       </c>
       <c r="C67">
-        <v>366560325.8630294</v>
+        <v>-1080762774.2303557</v>
       </c>
       <c r="D67">
-        <v>-1207725058.4343188</v>
+        <v>403371062.22700626</v>
       </c>
       <c r="E67">
-        <v>-340099295</v>
+        <v>-1329007274.7285237</v>
       </c>
       <c r="F67">
-        <v>82682484.37963958</v>
+        <v>-288582269</v>
       </c>
       <c r="G67">
-        <v>-551319497.616515</v>
+        <v>-374252760.6167274</v>
+      </c>
+      <c r="H67">
+        <v>90985628.28167449</v>
+      </c>
+      <c r="I67">
+        <v>-606684127.2482145</v>
       </c>
     </row>
     <row r="68">
@@ -3952,28 +4642,34 @@
       <c r="A75" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
+      <c r="F75">
+        <v>476188</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
       <c r="B76">
+        <v>-43274060</v>
+      </c>
+      <c r="C76">
         <v>0</v>
       </c>
-      <c r="C76">
-        <v>-320020430.397402</v>
-      </c>
       <c r="D76">
-        <v>-310384107.26590514</v>
+        <v>-352157535.4338237</v>
       </c>
       <c r="E76">
-        <v>-43274058</v>
-      </c>
-      <c r="F76">
-        <v>-1666230.4821692673</v>
+        <v>-341553513.0580716</v>
       </c>
       <c r="G76">
-        <v>21436093.47032249</v>
+        <v>-47619727.2610882</v>
+      </c>
+      <c r="H76">
+        <v>-1833556.7492887308</v>
+      </c>
+      <c r="I76">
+        <v>23588749.744707342</v>
       </c>
     </row>
     <row r="77">
@@ -3981,22 +4677,28 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>7605654</v>
+        <v>8821818</v>
       </c>
       <c r="C77">
-        <v>-833515.4433716835</v>
+        <v>8369429.303861555</v>
       </c>
       <c r="D77">
-        <v>2732466.7683299435</v>
+        <v>-917218.7660622116</v>
       </c>
       <c r="E77">
-        <v>6900464</v>
+        <v>3006866.6603409136</v>
       </c>
       <c r="F77">
-        <v>-6900464.193643421</v>
+        <v>6899175</v>
       </c>
       <c r="G77">
-        <v>6074957.397858354</v>
+        <v>7593422.684208579</v>
+      </c>
+      <c r="H77">
+        <v>-7593422.897298068</v>
+      </c>
+      <c r="I77">
+        <v>6685017.023565133</v>
       </c>
     </row>
     <row r="78">
@@ -4004,22 +4706,28 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-971259232</v>
+        <v>-1218320544</v>
       </c>
       <c r="C78">
-        <v>664477690.3889974</v>
+        <v>-1068795067.1890764</v>
       </c>
       <c r="D78">
-        <v>-900073417.9367436</v>
+        <v>731205896.7846711</v>
       </c>
       <c r="E78">
-        <v>-294195097</v>
+        <v>-990460628.3307931</v>
       </c>
       <c r="F78">
-        <v>91249179.05545227</v>
+        <v>-295957632</v>
       </c>
       <c r="G78">
-        <v>-578830548.4846959</v>
+        <v>-323738769.32663417</v>
+      </c>
+      <c r="H78">
+        <v>100412607.9282613</v>
+      </c>
+      <c r="I78">
+        <v>-636957894.016487</v>
       </c>
     </row>
     <row r="79">
@@ -4062,13 +4770,19 @@
         <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B86">
-        <v>-18481215</v>
+        <v>-21604938</v>
       </c>
       <c r="C86">
-        <v>22936581.314805686</v>
-      </c>
-      <c r="E86">
-        <v>-9530604</v>
+        <v>-20337136.345140826</v>
+      </c>
+      <c r="D86">
+        <v>25239919.64222118</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>-10487686.713213636</v>
       </c>
     </row>
     <row r="87">
@@ -4142,22 +4856,28 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>4036176204</v>
+        <v>3633261423</v>
       </c>
       <c r="C101">
-        <v>2806838313.090092</v>
+        <v>4441497259.447549</v>
       </c>
       <c r="D101">
-        <v>6764103785.719708</v>
+        <v>3088706747.477278</v>
       </c>
       <c r="E101">
-        <v>4084688391</v>
+        <v>7443368898.790742</v>
       </c>
       <c r="F101">
-        <v>2125904762.7770414</v>
+        <v>3479647584</v>
       </c>
       <c r="G101">
-        <v>179645208.99209175</v>
+        <v>4494881139.318</v>
+      </c>
+      <c r="H101">
+        <v>2339392459.715498</v>
+      </c>
+      <c r="I101">
+        <v>197685547.6776548</v>
       </c>
     </row>
     <row r="102">
@@ -4174,41 +4894,53 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>0</v>
       </c>
-      <c r="D104">
-        <v>2219383990.263466</v>
-      </c>
-      <c r="F104">
+      <c r="E104">
+        <v>2442259062.0914702</v>
+      </c>
+      <c r="H104">
         <v>0</v>
       </c>
-      <c r="G104">
-        <v>22437287.886672817</v>
+      <c r="I104">
+        <v>24690486.148580696</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
         <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>112000000</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
       <c r="B106">
-        <v>-1424027</v>
+        <v>-1567030</v>
       </c>
       <c r="C106">
+        <v>-1567030.6989103183</v>
+      </c>
+      <c r="D106">
         <v>0</v>
       </c>
-      <c r="D106">
-        <v>-57813080.4640425</v>
+      <c r="E106">
+        <v>-63618788.04666413</v>
       </c>
       <c r="F106">
         <v>0</v>
       </c>
-      <c r="G106">
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
         <v>0</v>
       </c>
     </row>
@@ -4227,22 +4959,28 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>4037600231</v>
+        <v>3854307425</v>
       </c>
       <c r="C109">
-        <v>2806838313.090092</v>
+        <v>4443064290.14646</v>
       </c>
       <c r="D109">
-        <v>4602532875.920285</v>
+        <v>3088706747.477278</v>
       </c>
       <c r="E109">
-        <v>4084688391</v>
+        <v>5064728624.745936</v>
       </c>
       <c r="F109">
-        <v>2125904762.7770414</v>
+        <v>3367647584</v>
       </c>
       <c r="G109">
-        <v>157207921.10541892</v>
+        <v>4494881139.318</v>
+      </c>
+      <c r="H109">
+        <v>2339392459.715498</v>
+      </c>
+      <c r="I109">
+        <v>172995061.52907407</v>
       </c>
     </row>
     <row r="110">
@@ -4284,6 +5022,12 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
+      <c r="B117">
+        <v>-219478972</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -4325,22 +5069,28 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>-175971929</v>
+        <v>289902869</v>
       </c>
       <c r="C125">
-        <v>922435491.0328045</v>
+        <v>-193643389.40867478</v>
       </c>
       <c r="D125">
-        <v>87657489.23294713</v>
+        <v>1015068346.4659154</v>
       </c>
       <c r="E125">
-        <v>250986882</v>
+        <v>96460233.2802881</v>
       </c>
       <c r="F125">
-        <v>417383151.7674402</v>
+        <v>-358391088</v>
       </c>
       <c r="G125">
-        <v>365163520.5652982</v>
+        <v>276191497.15404385</v>
+      </c>
+      <c r="H125">
+        <v>459297620.078498</v>
+      </c>
+      <c r="I125">
+        <v>401833986.88928765</v>
       </c>
     </row>
     <row r="126">
@@ -4348,22 +5098,28 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>-134735559</v>
+        <v>-467708163</v>
       </c>
       <c r="C126">
-        <v>-132656468.1888145</v>
+        <v>-148265978.93708646</v>
       </c>
       <c r="D126">
-        <v>85875620.79678306</v>
+        <v>-145978101.5815658</v>
       </c>
       <c r="E126">
-        <v>-91453234</v>
+        <v>94499425.9775555</v>
       </c>
       <c r="F126">
-        <v>-85459447.87271696</v>
+        <v>94589782</v>
       </c>
       <c r="G126">
-        <v>-66223501.5020928</v>
+        <v>-100637154.48697874</v>
+      </c>
+      <c r="H126">
+        <v>-94041460.11871515</v>
+      </c>
+      <c r="I126">
+        <v>-72873800.73770581</v>
       </c>
     </row>
     <row r="127">
@@ -4371,22 +5127,28 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>-310707488</v>
+        <v>-177805294</v>
       </c>
       <c r="C127">
-        <v>789779022.84399</v>
+        <v>-341909368.34576124</v>
       </c>
       <c r="D127">
-        <v>173533110.02973017</v>
+        <v>869090244.8843497</v>
       </c>
       <c r="E127">
-        <v>159533648</v>
+        <v>190959659.25784358</v>
       </c>
       <c r="F127">
-        <v>331923703.89472324</v>
+        <v>-263801306</v>
       </c>
       <c r="G127">
-        <v>298940019.0632054</v>
+        <v>175554342.66706508</v>
+      </c>
+      <c r="H127">
+        <v>365256159.95978284</v>
+      </c>
+      <c r="I127">
+        <v>328960186.1515818</v>
       </c>
     </row>
     <row r="128">
@@ -4394,22 +5156,28 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>586764338</v>
+        <v>645688410</v>
       </c>
       <c r="C128">
-        <v>586764337.7948931</v>
+        <v>645688410.8740847</v>
       </c>
       <c r="D128">
-        <v>549794165.9114033</v>
+        <v>645688410.6483806</v>
       </c>
       <c r="E128">
-        <v>549794166</v>
+        <v>605005618.6188617</v>
       </c>
       <c r="F128">
-        <v>549794166.0320383</v>
+        <v>605005619</v>
       </c>
       <c r="G128">
-        <v>565481240.6119463</v>
+        <v>605005618.7163554</v>
+      </c>
+      <c r="H128">
+        <v>605005618.7516111</v>
+      </c>
+      <c r="I128">
+        <v>622268021.3906142</v>
       </c>
     </row>
     <row r="129">
@@ -4417,34 +5185,40 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>212318593</v>
+        <v>345220787</v>
       </c>
       <c r="C129">
-        <v>1335584065.3548653</v>
+        <v>233640059.61996886</v>
       </c>
       <c r="D129">
-        <v>580641316.147658</v>
+        <v>1469706144.1858327</v>
       </c>
       <c r="E129">
-        <v>579569087</v>
+        <v>638950502.6653789</v>
       </c>
       <c r="F129">
-        <v>744390971.1300746</v>
+        <v>198501319</v>
       </c>
       <c r="G129">
-        <v>542955762.965235</v>
+        <v>637770598.0774417</v>
+      </c>
+      <c r="H129">
+        <v>819144232.3442543</v>
+      </c>
+      <c r="I129">
+        <v>597480489.2862265</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:I129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4453,6 +5227,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4460,21 +5236,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -4488,16 +5270,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-979050192.0796828</v>
+        <v>1485397044.6258683</v>
       </c>
       <c r="C3">
-        <v>-2250963147.920317</v>
+        <v>-1077368411.3874993</v>
+      </c>
+      <c r="D3">
+        <v>-2477009463.238369</v>
       </c>
       <c r="E3">
-        <v>-1702398118.610759</v>
+        <v>-2468444987.78193</v>
       </c>
       <c r="F3">
-        <v>-1791204095.389241</v>
+        <v>294980478.54722834</v>
+      </c>
+      <c r="G3">
+        <v>-1873356413.6285536</v>
+      </c>
+      <c r="H3">
+        <v>-1971080467.9186747</v>
       </c>
     </row>
     <row r="4">
@@ -4505,16 +5296,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-39136923.39178312</v>
+        <v>697553754.9527444</v>
       </c>
       <c r="C4">
-        <v>-740900402.6082169</v>
+        <v>-43067133.14833593</v>
+      </c>
+      <c r="D4">
+        <v>-815303133.8044084</v>
       </c>
       <c r="E4">
-        <v>-100703969.52626497</v>
+        <v>915506774.6710874</v>
       </c>
       <c r="F4">
-        <v>304572871.52626497</v>
+        <v>-553757931.3972173</v>
+      </c>
+      <c r="G4">
+        <v>-110816867.76289102</v>
+      </c>
+      <c r="H4">
+        <v>335158701.1601083</v>
       </c>
     </row>
     <row r="5">
@@ -4522,16 +5322,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>-226308693.00034153</v>
+        <v>255150764.53444207</v>
       </c>
       <c r="C5">
-        <v>134451832.00034153</v>
+        <v>-249035074.0272522</v>
+      </c>
+      <c r="D5">
+        <v>147953759.4928101</v>
       </c>
       <c r="E5">
-        <v>-582698737.0627342</v>
+        <v>-1340840597.842598</v>
       </c>
       <c r="F5">
-        <v>582033283.0627342</v>
+        <v>1913520449.2494001</v>
+      </c>
+      <c r="G5">
+        <v>-641214533.9895777</v>
+      </c>
+      <c r="H5">
+        <v>640482253.7401774</v>
       </c>
     </row>
     <row r="6">
@@ -4539,16 +5348,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>32444728.491889454</v>
+        <v>20901341.054757297</v>
       </c>
       <c r="C6">
-        <v>46685219.508110546</v>
+        <v>35702894.372509114</v>
+      </c>
+      <c r="D6">
+        <v>51373444.57273359</v>
       </c>
       <c r="E6">
-        <v>30247387.95512916</v>
+        <v>98433091.64906758</v>
       </c>
       <c r="F6">
-        <v>44013541.04487084</v>
+        <v>-19943807.115727097</v>
+      </c>
+      <c r="G6">
+        <v>33284892.412529804</v>
+      </c>
+      <c r="H6">
+        <v>48433470.70319729</v>
       </c>
     </row>
     <row r="7">
@@ -4561,16 +5379,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>-3092212.0518825613</v>
+        <v>-7317160.347095937</v>
       </c>
       <c r="C8">
-        <v>19760578.05188256</v>
+        <v>-3402738.2997937836</v>
+      </c>
+      <c r="D8">
+        <v>21744975.64688972</v>
       </c>
       <c r="E8">
-        <v>3709089.278238427</v>
+        <v>41945050.79744713</v>
       </c>
       <c r="F8">
-        <v>27394449.721761573</v>
+        <v>-48647801.893410966</v>
+      </c>
+      <c r="G8">
+        <v>4081563.5967567526</v>
+      </c>
+      <c r="H8">
+        <v>30145456.296654213</v>
       </c>
     </row>
     <row r="9">
@@ -4632,6 +5459,12 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B20">
+        <v>-32938990.222501118</v>
+      </c>
+      <c r="F20">
+        <v>7463836.747657143</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -4643,16 +5476,25 @@
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B22">
-        <v>93607.63105766775</v>
+        <v>-34668538.44215352</v>
       </c>
       <c r="C22">
-        <v>98416.36894233225</v>
+        <v>103007.90049601327</v>
+      </c>
+      <c r="D22">
+        <v>108299.54165750976</v>
       </c>
       <c r="E22">
-        <v>301484.6635325281</v>
+        <v>199277.05771078868</v>
       </c>
       <c r="F22">
-        <v>-2646907.663532528</v>
+        <v>-648319.8334685117</v>
+      </c>
+      <c r="G22">
+        <v>331760.36901415465</v>
+      </c>
+      <c r="H22">
+        <v>-2912715.535545643</v>
       </c>
     </row>
     <row r="23">
@@ -4679,11 +5521,11 @@
       <c r="A27" t="str">
         <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
       </c>
-      <c r="C27">
-        <v>38878243.39135845</v>
-      </c>
-      <c r="F27">
-        <v>55596369.90989303</v>
+      <c r="D27">
+        <v>42782475.97409733</v>
+      </c>
+      <c r="H27">
+        <v>61179470.89259983</v>
       </c>
     </row>
     <row r="28">
@@ -4691,16 +5533,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-965136327.4653156</v>
+        <v>525872879.5186901</v>
       </c>
       <c r="C28">
-        <v>-1641114838.5346844</v>
+        <v>-1062057288.0793068</v>
+      </c>
+      <c r="D28">
+        <v>-1805918941.4393833</v>
       </c>
       <c r="E28">
-        <v>-1021633454.8196611</v>
+        <v>-2763019243.557249</v>
       </c>
       <c r="F28">
-        <v>-2676478075.180339</v>
+        <v>-329674124.37408066</v>
+      </c>
+      <c r="G28">
+        <v>-1124227972.3180923</v>
+      </c>
+      <c r="H28">
+        <v>-2945255468.307827</v>
       </c>
     </row>
     <row r="29">
@@ -4718,16 +5569,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-1867661741.6070228</v>
+        <v>-4590522022.262147</v>
       </c>
       <c r="C31">
-        <v>2526676715.607023</v>
+        <v>-2055216147.0804381</v>
+      </c>
+      <c r="D31">
+        <v>2780410750.342585</v>
       </c>
       <c r="E31">
-        <v>-8163795.825205952</v>
+        <v>-1422667394.17977</v>
       </c>
       <c r="F31">
-        <v>-178203507.17479405</v>
+        <v>-1249987058.909029</v>
+      </c>
+      <c r="G31">
+        <v>-8983620.870765537</v>
+      </c>
+      <c r="H31">
+        <v>-196099067.2202054</v>
       </c>
     </row>
     <row r="32">
@@ -4740,16 +5600,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-794612654.224969</v>
+        <v>72353522.99484324</v>
       </c>
       <c r="C33">
-        <v>-555816858.775031</v>
+        <v>-874409279.397888</v>
+      </c>
+      <c r="D33">
+        <v>-611633122.5969553</v>
       </c>
       <c r="E33">
-        <v>-504090898.6218869</v>
+        <v>823711155.1937603</v>
       </c>
       <c r="F33">
-        <v>-145645739.3781131</v>
+        <v>-540659918.1834273</v>
+      </c>
+      <c r="G33">
+        <v>-554712735.911458</v>
+      </c>
+      <c r="H33">
+        <v>-160271781.9051146</v>
       </c>
     </row>
     <row r="34">
@@ -4772,16 +5641,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>438527785.4310703</v>
+        <v>4559071336.945226</v>
       </c>
       <c r="C37">
-        <v>-7364885042.43107</v>
+        <v>482565641.02762413</v>
+      </c>
+      <c r="D37">
+        <v>-8104481835.97285</v>
       </c>
       <c r="E37">
-        <v>1890280682.8753366</v>
+        <v>-23278744.133396626</v>
       </c>
       <c r="F37">
-        <v>-5043191545.875337</v>
+        <v>-75661466.54187536</v>
+      </c>
+      <c r="G37">
+        <v>2080106528.614143</v>
+      </c>
+      <c r="H37">
+        <v>-5549639138.072268</v>
       </c>
     </row>
     <row r="38">
@@ -4799,16 +5677,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>1211085319.3823628</v>
+        <v>606268087.7041492</v>
       </c>
       <c r="C40">
-        <v>3746622006.617637</v>
+        <v>1332704979.9419327</v>
+      </c>
+      <c r="D40">
+        <v>4122865438.353918</v>
       </c>
       <c r="E40">
-        <v>-2305892001.3832</v>
+        <v>-2329535630.031802</v>
       </c>
       <c r="F40">
-        <v>2558804312.3832</v>
+        <v>1558904591.334446</v>
+      </c>
+      <c r="G40">
+        <v>-2537454384.3194184</v>
+      </c>
+      <c r="H40">
+        <v>2815764665.9849725</v>
       </c>
     </row>
     <row r="41">
@@ -4831,16 +5718,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>47524963.553242736</v>
+        <v>-121298045.8633814</v>
       </c>
       <c r="C44">
-        <v>6288340.446757265</v>
+        <v>52297517.42946262</v>
+      </c>
+      <c r="D44">
+        <v>6919828.433918782</v>
       </c>
       <c r="E44">
-        <v>-93767441.86470442</v>
+        <v>188751369.5939588</v>
       </c>
       <c r="F44">
-        <v>131758404.86470442</v>
+        <v>-22270272.07419455</v>
+      </c>
+      <c r="G44">
+        <v>-103183759.83059338</v>
+      </c>
+      <c r="H44">
+        <v>144989852.90478793</v>
       </c>
     </row>
     <row r="45">
@@ -4868,16 +5764,25 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-1230581943.8574405</v>
+        <v>1478577399.0058765</v>
       </c>
       <c r="C49">
-        <v>-2247563409.1425595</v>
+        <v>-1354159495.2548952</v>
+      </c>
+      <c r="D49">
+        <v>-2473268315.7509813</v>
       </c>
       <c r="E49">
-        <v>-1705036161.4086607</v>
+        <v>-3188353066.7287607</v>
       </c>
       <c r="F49">
-        <v>-1789871920.5913393</v>
+        <v>1030088393.4781027</v>
+      </c>
+      <c r="G49">
+        <v>-1876259374.070562</v>
+      </c>
+      <c r="H49">
+        <v>-1969614513.4075408</v>
       </c>
     </row>
     <row r="50">
@@ -4929,6 +5834,12 @@
       <c r="A59" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
+      <c r="B59">
+        <v>6194203.190843701</v>
+      </c>
+      <c r="F59">
+        <v>-819955528.5923383</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -4945,16 +5856,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-25694605.22224268</v>
+        <v>625442.4291479178</v>
       </c>
       <c r="C62">
-        <v>-3399738.777757319</v>
+        <v>-28274909.941760696</v>
+      </c>
+      <c r="D62">
+        <v>-3741147.487387222</v>
       </c>
       <c r="E62">
-        <v>78598.79790153308</v>
+        <v>-12509488.053170804</v>
       </c>
       <c r="F62">
-        <v>-1332174.797901533</v>
+        <v>126120.66146442527</v>
+      </c>
+      <c r="G62">
+        <v>86491.8496693885</v>
+      </c>
+      <c r="H62">
+        <v>-1465954.5111338138</v>
       </c>
     </row>
     <row r="63">
@@ -4978,16 +5898,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-1348695118.8630295</v>
+        <v>-193614949.76964426</v>
       </c>
       <c r="C67">
-        <v>366560325.8630294</v>
+        <v>-1484133836.457362</v>
+      </c>
+      <c r="D67">
+        <v>403371062.22700626</v>
       </c>
       <c r="E67">
-        <v>-422781779.37963957</v>
+        <v>-1040425005.7285237</v>
       </c>
       <c r="F67">
-        <v>82682484.37963958</v>
+        <v>85670491.61672741</v>
+      </c>
+      <c r="G67">
+        <v>-465238388.8984019</v>
+      </c>
+      <c r="H67">
+        <v>90985628.28167449</v>
       </c>
     </row>
     <row r="68">
@@ -5035,16 +5964,19 @@
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
       <c r="B76">
-        <v>320020430.397402</v>
+        <v>-43274060</v>
       </c>
       <c r="C76">
-        <v>-320020430.397402</v>
-      </c>
-      <c r="E76">
-        <v>-41607827.51783073</v>
-      </c>
-      <c r="F76">
-        <v>-1666230.4821692673</v>
+        <v>352157535.4338237</v>
+      </c>
+      <c r="D76">
+        <v>-352157535.4338237</v>
+      </c>
+      <c r="G76">
+        <v>-45786170.51179947</v>
+      </c>
+      <c r="H76">
+        <v>-1833556.7492887308</v>
       </c>
     </row>
     <row r="77">
@@ -5052,16 +5984,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>8439169.443371683</v>
+        <v>452388.6961384453</v>
       </c>
       <c r="C77">
-        <v>-833515.4433716835</v>
+        <v>9286648.069923766</v>
+      </c>
+      <c r="D77">
+        <v>-917218.7660622116</v>
       </c>
       <c r="E77">
-        <v>13800928.193643421</v>
+        <v>-3892308.3396590864</v>
       </c>
       <c r="F77">
-        <v>-6900464.193643421</v>
+        <v>-694247.6842085794</v>
+      </c>
+      <c r="G77">
+        <v>15186845.581506647</v>
+      </c>
+      <c r="H77">
+        <v>-7593422.897298068</v>
       </c>
     </row>
     <row r="78">
@@ -5069,16 +6010,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-1635736922.3889976</v>
+        <v>-149525476.81092358</v>
       </c>
       <c r="C78">
-        <v>664477690.3889974</v>
+        <v>-1800000963.9737475</v>
+      </c>
+      <c r="D78">
+        <v>731205896.7846711</v>
       </c>
       <c r="E78">
-        <v>-385444276.0554523</v>
+        <v>-694502996.3307931</v>
       </c>
       <c r="F78">
-        <v>91249179.05545227</v>
+        <v>27781137.32663417</v>
+      </c>
+      <c r="G78">
+        <v>-424151377.25489545</v>
+      </c>
+      <c r="H78">
+        <v>100412607.9282613</v>
       </c>
     </row>
     <row r="79">
@@ -5121,10 +6071,16 @@
         <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B86">
-        <v>-41417796.31480569</v>
+        <v>-1267801.654859174</v>
       </c>
       <c r="C86">
-        <v>22936581.314805686</v>
+        <v>-45577055.987362005</v>
+      </c>
+      <c r="D86">
+        <v>25239919.64222118</v>
+      </c>
+      <c r="F86">
+        <v>10487686.713213636</v>
       </c>
     </row>
     <row r="87">
@@ -5198,16 +6154,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>1229337890.9099078</v>
+        <v>-808235836.4475489</v>
       </c>
       <c r="C101">
-        <v>2806838313.090092</v>
+        <v>1352790511.9702706</v>
+      </c>
+      <c r="D101">
+        <v>3088706747.477278</v>
       </c>
       <c r="E101">
-        <v>1958783628.2229586</v>
+        <v>3963721314.790742</v>
       </c>
       <c r="F101">
-        <v>2125904762.7770414</v>
+        <v>-1015233555.3179998</v>
+      </c>
+      <c r="G101">
+        <v>2155488679.602502</v>
+      </c>
+      <c r="H101">
+        <v>2339392459.715498</v>
       </c>
     </row>
     <row r="102">
@@ -5224,10 +6189,10 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>0</v>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>0</v>
       </c>
     </row>
@@ -5241,12 +6206,18 @@
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
       <c r="B106">
-        <v>-1424027</v>
+        <v>0.6989103183150291</v>
       </c>
       <c r="C106">
+        <v>-1567030.6989103183</v>
+      </c>
+      <c r="D106">
         <v>0</v>
       </c>
-      <c r="F106">
+      <c r="E106">
+        <v>-63618788.04666413</v>
+      </c>
+      <c r="H106">
         <v>0</v>
       </c>
     </row>
@@ -5265,16 +6236,25 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>1230761917.9099078</v>
+        <v>-588756865.1464596</v>
       </c>
       <c r="C109">
-        <v>2806838313.090092</v>
+        <v>1354357542.6691813</v>
+      </c>
+      <c r="D109">
+        <v>3088706747.477278</v>
       </c>
       <c r="E109">
-        <v>1958783628.2229586</v>
+        <v>1697081040.7459364</v>
       </c>
       <c r="F109">
-        <v>2125904762.7770414</v>
+        <v>-1127233555.3179998</v>
+      </c>
+      <c r="G109">
+        <v>2155488679.602502</v>
+      </c>
+      <c r="H109">
+        <v>2339392459.715498</v>
       </c>
     </row>
     <row r="110">
@@ -5357,16 +6337,25 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>-1098407420.0328045</v>
+        <v>483546258.4086748</v>
       </c>
       <c r="C125">
-        <v>922435491.0328045</v>
+        <v>-1208711735.8745902</v>
+      </c>
+      <c r="D125">
+        <v>1015068346.4659154</v>
       </c>
       <c r="E125">
-        <v>-166396269.7674402</v>
+        <v>454851321.2802881</v>
       </c>
       <c r="F125">
-        <v>417383151.7674402</v>
+        <v>-634582585.1540439</v>
+      </c>
+      <c r="G125">
+        <v>-183106122.92445415</v>
+      </c>
+      <c r="H125">
+        <v>459297620.078498</v>
       </c>
     </row>
     <row r="126">
@@ -5374,16 +6363,25 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>-2079090.811185494</v>
+        <v>-319442184.06291354</v>
       </c>
       <c r="C126">
-        <v>-132656468.1888145</v>
+        <v>-2287877.3555206656</v>
+      </c>
+      <c r="D126">
+        <v>-145978101.5815658</v>
       </c>
       <c r="E126">
-        <v>-5993786.127283037</v>
+        <v>-90356.02244450152</v>
       </c>
       <c r="F126">
-        <v>-85459447.87271696</v>
+        <v>195226936.48697874</v>
+      </c>
+      <c r="G126">
+        <v>-6595694.368263587</v>
+      </c>
+      <c r="H126">
+        <v>-94041460.11871515</v>
       </c>
     </row>
     <row r="127">
@@ -5391,16 +6389,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>-1100486510.8439898</v>
+        <v>164104074.34576124</v>
       </c>
       <c r="C127">
-        <v>789779022.84399</v>
+        <v>-1210999613.230111</v>
+      </c>
+      <c r="D127">
+        <v>869090244.8843497</v>
       </c>
       <c r="E127">
-        <v>-172390055.89472324</v>
+        <v>454760965.2578436</v>
       </c>
       <c r="F127">
-        <v>331923703.89472324</v>
+        <v>-439355648.6670651</v>
+      </c>
+      <c r="G127">
+        <v>-189701817.29271775</v>
+      </c>
+      <c r="H127">
+        <v>365256159.95978284</v>
       </c>
     </row>
     <row r="128">
@@ -5408,16 +6415,25 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>0.20510685443878174</v>
+        <v>-0.8740847110748291</v>
       </c>
       <c r="C128">
-        <v>586764337.7948931</v>
+        <v>0.22570407390594482</v>
+      </c>
+      <c r="D128">
+        <v>645688410.6483806</v>
       </c>
       <c r="E128">
-        <v>-0.032038331031799316</v>
+        <v>-0.38113832473754883</v>
       </c>
       <c r="F128">
-        <v>549794166.0320383</v>
+        <v>0.28364455699920654</v>
+      </c>
+      <c r="G128">
+        <v>-0.03525567054748535</v>
+      </c>
+      <c r="H128">
+        <v>605005618.7516111</v>
       </c>
     </row>
     <row r="129">
@@ -5425,28 +6441,37 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>-1123265472.3548653</v>
+        <v>111580727.38003114</v>
       </c>
       <c r="C129">
-        <v>1335584065.3548653</v>
+        <v>-1236066084.5658638</v>
+      </c>
+      <c r="D129">
+        <v>1469706144.1858327</v>
       </c>
       <c r="E129">
-        <v>-164821884.13007462</v>
+        <v>440449183.6653789</v>
       </c>
       <c r="F129">
-        <v>744390971.1300746</v>
+        <v>-439269279.0774417</v>
+      </c>
+      <c r="G129">
+        <v>-181373634.26681256</v>
+      </c>
+      <c r="H129">
+        <v>819144232.3442543</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:I129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5455,6 +6480,8 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5462,21 +6489,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/9</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2024/9</v>
+      </c>
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -5490,16 +6523,19 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-5205132364.052443</v>
+        <v>-4537425817.78193</v>
       </c>
       <c r="C3">
-        <v>-5928480290.583519</v>
+        <v>-5727842383.86057</v>
       </c>
       <c r="D3">
-        <v>-5468721238.052443</v>
-      </c>
-      <c r="G3">
-        <v>736837809.1897215</v>
+        <v>-6523830386.1016245</v>
+      </c>
+      <c r="E3">
+        <v>-6017901390.78193</v>
+      </c>
+      <c r="I3">
+        <v>810832566.4598473</v>
       </c>
     </row>
     <row r="4">
@@ -5507,16 +6543,19 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>-451300868.9548524</v>
+        <v>754690262.6710874</v>
       </c>
       <c r="C4">
-        <v>-512867915.08933425</v>
+        <v>-496621423.67887425</v>
       </c>
       <c r="D4">
-        <v>532605359.0451476</v>
-      </c>
-      <c r="G4">
-        <v>1730128743.6095934</v>
+        <v>-564371158.2934294</v>
+      </c>
+      <c r="E4">
+        <v>586090676.6710874</v>
+      </c>
+      <c r="I4">
+        <v>1903871804.6100051</v>
       </c>
     </row>
     <row r="5">
@@ -5524,16 +6563,19 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>428561514.54705524</v>
+        <v>-1186771147.842598</v>
       </c>
       <c r="C5">
-        <v>72171470.48466253</v>
+        <v>471598536.8723602</v>
       </c>
       <c r="D5">
-        <v>519752921.54705524</v>
-      </c>
-      <c r="G5">
-        <v>-32917764.130232394</v>
+        <v>79419076.91003475</v>
+      </c>
+      <c r="E5">
+        <v>571947571.157402</v>
+      </c>
+      <c r="I5">
+        <v>-36223433.21549597</v>
       </c>
     </row>
     <row r="6">
@@ -5541,16 +6583,19 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>150456476.87009963</v>
+        <v>206410771.64906758</v>
       </c>
       <c r="C6">
-        <v>148259136.33333933</v>
+        <v>165565623.4785832</v>
       </c>
       <c r="D6">
-        <v>145587457.87009963</v>
-      </c>
-      <c r="G6">
-        <v>142093231.71564442</v>
+        <v>163147621.51860386</v>
+      </c>
+      <c r="E6">
+        <v>160207647.64906758</v>
+      </c>
+      <c r="I6">
+        <v>156362524.16969067</v>
       </c>
     </row>
     <row r="7">
@@ -5563,16 +6608,19 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>10577292.901324</v>
+        <v>52970127.79744713</v>
       </c>
       <c r="C8">
-        <v>17378594.23144499</v>
+        <v>11639486.251132105</v>
       </c>
       <c r="D8">
-        <v>25012465.901324</v>
-      </c>
-      <c r="G8">
-        <v>14290766.375694806</v>
+        <v>19123788.14768264</v>
+      </c>
+      <c r="E8">
+        <v>27524268.797447134</v>
+      </c>
+      <c r="I8">
+        <v>15725874.313948477</v>
       </c>
     </row>
     <row r="9">
@@ -5645,16 +6693,19 @@
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B22">
-        <v>-216040.14148657303</v>
+        <v>-34257953.94228921</v>
       </c>
       <c r="C22">
-        <v>-8163.109011712688</v>
+        <v>-237735.3336042</v>
       </c>
       <c r="D22">
-        <v>-2753487.141486573</v>
-      </c>
-      <c r="G22">
-        <v>-12620282.245922156</v>
+        <v>-8982.865086058606</v>
+      </c>
+      <c r="E22">
+        <v>-3029997.9422892113</v>
+      </c>
+      <c r="I22">
+        <v>-13887636.757078957</v>
       </c>
     </row>
     <row r="23">
@@ -5681,14 +6732,14 @@
       <c r="A27" t="str">
         <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
       </c>
-      <c r="C27">
-        <v>205793379.6261319</v>
-      </c>
       <c r="D27">
-        <v>222511506.14466646</v>
-      </c>
-      <c r="G27">
-        <v>-453503314.2605063</v>
+        <v>226459570.99595296</v>
+      </c>
+      <c r="E27">
+        <v>244856565.91445544</v>
+      </c>
+      <c r="I27">
+        <v>-499045043.0390623</v>
       </c>
     </row>
     <row r="28">
@@ -5696,16 +6747,19 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-5416712289.523397</v>
+        <v>-5105122593.557249</v>
       </c>
       <c r="C28">
-        <v>-5473209416.877743</v>
+        <v>-5960669597.45002</v>
       </c>
       <c r="D28">
-        <v>-6508572653.523397</v>
-      </c>
-      <c r="G28">
-        <v>-951517788.6643221</v>
+        <v>-6022840281.688806</v>
+      </c>
+      <c r="E28">
+        <v>-7162176808.557249</v>
+      </c>
+      <c r="I28">
+        <v>-1047071147.8056618</v>
       </c>
     </row>
     <row r="29">
@@ -5723,16 +6777,19 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-1769739041.8053393</v>
+        <v>-5287994813.1797695</v>
       </c>
       <c r="C31">
-        <v>89758903.97647762</v>
+        <v>-1947459849.826652</v>
       </c>
       <c r="D31">
-        <v>-2615121318.8053393</v>
-      </c>
-      <c r="G31">
-        <v>-656390342.7272944</v>
+        <v>98772676.3830204</v>
+      </c>
+      <c r="E31">
+        <v>-2877737141.17977</v>
+      </c>
+      <c r="I31">
+        <v>-722306401.1580788</v>
       </c>
     </row>
     <row r="32">
@@ -5745,16 +6802,19 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1093208895.5823567</v>
+        <v>-589977723.8062397</v>
       </c>
       <c r="C33">
-        <v>-802687139.9792745</v>
+        <v>-1202991164.9845104</v>
       </c>
       <c r="D33">
-        <v>-392516020.58235663</v>
-      </c>
-      <c r="G33">
-        <v>111897842.06165054</v>
+        <v>-883294621.4980805</v>
+      </c>
+      <c r="E33">
+        <v>-431933280.8062397</v>
+      </c>
+      <c r="I33">
+        <v>123134851.83386597</v>
       </c>
     </row>
     <row r="34">
@@ -5777,16 +6837,19 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-7016268406.465834</v>
+        <v>-3086123602.1333966</v>
       </c>
       <c r="C37">
-        <v>-5564515509.021567</v>
+        <v>-7720856405.620498</v>
       </c>
       <c r="D37">
-        <v>-3242822012.4658337</v>
-      </c>
-      <c r="G37">
-        <v>-930356222.1424795</v>
+        <v>-6123315518.033979</v>
+      </c>
+      <c r="E37">
+        <v>-3568472820.1333966</v>
+      </c>
+      <c r="I37">
+        <v>-1023784493.5661284</v>
       </c>
     </row>
     <row r="38">
@@ -5804,16 +6867,19 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>4257402343.5218716</v>
+        <v>3732302875.968198</v>
       </c>
       <c r="C40">
-        <v>740425022.7563086</v>
+        <v>4684939379.598495</v>
       </c>
       <c r="D40">
-        <v>-447392671.4781286</v>
-      </c>
-      <c r="G40">
-        <v>636730897.6581092</v>
+        <v>814780015.3371434</v>
+      </c>
+      <c r="E40">
+        <v>-492320757.03180224</v>
+      </c>
+      <c r="I40">
+        <v>700672714.4745016</v>
       </c>
     </row>
     <row r="41">
@@ -5836,16 +6902,19 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>205101710.8082607</v>
+        <v>126670669.5939588</v>
       </c>
       <c r="C44">
-        <v>63809305.39031356</v>
+        <v>225698443.38314563</v>
       </c>
       <c r="D44">
-        <v>189279369.8082607</v>
-      </c>
-      <c r="G44">
-        <v>-113399963.51430798</v>
+        <v>70217166.12308964</v>
+      </c>
+      <c r="E44">
+        <v>208287190.5939588</v>
+      </c>
+      <c r="I44">
+        <v>-124787819.3898224</v>
       </c>
     </row>
     <row r="45">
@@ -5873,16 +6942,19 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-5439451643.931195</v>
+        <v>-5537203478.728761</v>
       </c>
       <c r="C49">
-        <v>-5913905861.482416</v>
+        <v>-5985692484.256535</v>
       </c>
       <c r="D49">
-        <v>-5456214372.931195</v>
-      </c>
-      <c r="G49">
-        <v>745693190.8150387</v>
+        <v>-6507792363.072201</v>
+      </c>
+      <c r="E49">
+        <v>-6004138560.728761</v>
+      </c>
+      <c r="I49">
+        <v>820577223.5888473</v>
       </c>
     </row>
     <row r="50">
@@ -5950,16 +7022,19 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
       <c r="B62">
-        <v>-40347633.12124821</v>
+        <v>-43900103.0531708</v>
       </c>
       <c r="C62">
-        <v>-14574429.101103993</v>
+        <v>-44399424.8208543</v>
       </c>
       <c r="D62">
-        <v>-12506865.121248208</v>
-      </c>
-      <c r="G62">
-        <v>-8855381.625317274</v>
+        <v>-16038023.029424211</v>
+      </c>
+      <c r="E62">
+        <v>-13762830.053170804</v>
+      </c>
+      <c r="I62">
+        <v>-9744657.129000025</v>
       </c>
     </row>
     <row r="63">
@@ -5983,16 +7058,19 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-1849760556.4343188</v>
+        <v>-2314802729.7285237</v>
       </c>
       <c r="C67">
-        <v>-923847216.9509289</v>
+        <v>-2035517288.342152</v>
       </c>
       <c r="D67">
-        <v>-1207725058.4343188</v>
-      </c>
-      <c r="G67">
-        <v>-551319497.616515</v>
+        <v>-1016621840.7831919</v>
+      </c>
+      <c r="E67">
+        <v>-1329007274.7285237</v>
+      </c>
+      <c r="I67">
+        <v>-606684127.2482145</v>
       </c>
     </row>
     <row r="68">
@@ -6039,17 +7117,17 @@
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
-      <c r="B76">
-        <v>-267110049.26590514</v>
-      </c>
       <c r="C76">
-        <v>-628738307.1811378</v>
+        <v>-293933785.7969834</v>
       </c>
       <c r="D76">
-        <v>-310384107.26590514</v>
-      </c>
-      <c r="G76">
-        <v>21436093.47032249</v>
+        <v>-691877491.7426066</v>
+      </c>
+      <c r="E76">
+        <v>-341553513.0580716</v>
+      </c>
+      <c r="I76">
+        <v>23588749.744707342</v>
       </c>
     </row>
     <row r="77">
@@ -6057,16 +7135,19 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>3437656.7683299435</v>
+        <v>4929509.660340914</v>
       </c>
       <c r="C77">
-        <v>8799415.518601682</v>
+        <v>3782873.279993889</v>
       </c>
       <c r="D77">
-        <v>2732466.7683299435</v>
-      </c>
-      <c r="G77">
-        <v>6074957.397858354</v>
+        <v>9683070.79157677</v>
+      </c>
+      <c r="E77">
+        <v>3006866.6603409136</v>
+      </c>
+      <c r="I77">
+        <v>6685017.023565133</v>
       </c>
     </row>
     <row r="78">
@@ -6074,16 +7155,19 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-1577137552.9367437</v>
+        <v>-1912823540.3307931</v>
       </c>
       <c r="C78">
-        <v>-326844906.6031984</v>
+        <v>-1735516926.1932354</v>
       </c>
       <c r="D78">
-        <v>-900073417.9367436</v>
-      </c>
-      <c r="G78">
-        <v>-578830548.4846959</v>
+        <v>-359667339.47438335</v>
+      </c>
+      <c r="E78">
+        <v>-990460628.3307931</v>
+      </c>
+      <c r="I78">
+        <v>-636957894.016487</v>
       </c>
     </row>
     <row r="79">
@@ -6197,16 +7281,19 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>6715591598.719708</v>
+        <v>7596982737.790742</v>
       </c>
       <c r="C101">
-        <v>7445037336.032759</v>
+        <v>7389985018.920291</v>
       </c>
       <c r="D101">
-        <v>6764103785.719708</v>
-      </c>
-      <c r="G101">
-        <v>179645208.99209175</v>
+        <v>8192683186.552523</v>
+      </c>
+      <c r="E101">
+        <v>7443368898.790742</v>
+      </c>
+      <c r="I101">
+        <v>197685547.6776548</v>
       </c>
     </row>
     <row r="102">
@@ -6223,14 +7310,14 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C104">
-        <v>2219383990.263466</v>
-      </c>
       <c r="D104">
-        <v>2219383990.263466</v>
-      </c>
-      <c r="G104">
-        <v>22437287.886672817</v>
+        <v>2442259062.0914702</v>
+      </c>
+      <c r="E104">
+        <v>2442259062.0914702</v>
+      </c>
+      <c r="I104">
+        <v>24690486.148580696</v>
       </c>
     </row>
     <row r="105">
@@ -6242,13 +7329,16 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="C106">
-        <v>-57813080.4640425</v>
+      <c r="B106">
+        <v>-65185818.04666413</v>
       </c>
       <c r="D106">
-        <v>-57813080.4640425</v>
-      </c>
-      <c r="G106">
+        <v>-63618788.04666413</v>
+      </c>
+      <c r="E106">
+        <v>-63618788.04666413</v>
+      </c>
+      <c r="I106">
         <v>0</v>
       </c>
     </row>
@@ -6267,16 +7357,19 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>4555444715.920285</v>
+        <v>5551388465.745936</v>
       </c>
       <c r="C109">
-        <v>5283466426.2333355</v>
+        <v>5012911775.574396</v>
       </c>
       <c r="D109">
-        <v>4602532875.920285</v>
-      </c>
-      <c r="G109">
-        <v>157207921.10541892</v>
+        <v>5814042912.507717</v>
+      </c>
+      <c r="E109">
+        <v>5064728624.745936</v>
+      </c>
+      <c r="I109">
+        <v>172995061.52907407</v>
       </c>
     </row>
     <row r="110">
@@ -6359,16 +7452,19 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>-339301321.7670529</v>
+        <v>744754190.2802881</v>
       </c>
       <c r="C125">
-        <v>592709828.4983114</v>
+        <v>-373374653.2824305</v>
       </c>
       <c r="D125">
-        <v>87657489.23294713</v>
-      </c>
-      <c r="G125">
-        <v>365163520.5652982</v>
+        <v>652230959.6677055</v>
+      </c>
+      <c r="E125">
+        <v>96460233.2802881</v>
+      </c>
+      <c r="I125">
+        <v>401833986.88928765</v>
       </c>
     </row>
     <row r="126">
@@ -6376,16 +7472,19 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
       <c r="B126">
-        <v>42593295.79678306</v>
+        <v>-467798519.0224445</v>
       </c>
       <c r="C126">
-        <v>38678600.48068552</v>
+        <v>46870601.52744776</v>
       </c>
       <c r="D126">
-        <v>85875620.79678306</v>
-      </c>
-      <c r="G126">
-        <v>-66223501.5020928</v>
+        <v>42562784.51470485</v>
+      </c>
+      <c r="E126">
+        <v>94499425.9775555</v>
+      </c>
+      <c r="I126">
+        <v>-72873800.73770581</v>
       </c>
     </row>
     <row r="127">
@@ -6393,16 +7492,19 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>-296708025.9702698</v>
+        <v>276955671.2578436</v>
       </c>
       <c r="C127">
-        <v>631388428.9789969</v>
+        <v>-326504051.7549827</v>
       </c>
       <c r="D127">
-        <v>173533110.02973017</v>
-      </c>
-      <c r="G127">
-        <v>298940019.0632054</v>
+        <v>694793744.1824105</v>
+      </c>
+      <c r="E127">
+        <v>190959659.25784358</v>
+      </c>
+      <c r="I127">
+        <v>328960186.1515818</v>
       </c>
     </row>
     <row r="128">
@@ -6410,16 +7512,19 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>586764337.9114033</v>
+        <v>645688409.6188617</v>
       </c>
       <c r="C128">
-        <v>586764337.6742581</v>
+        <v>645688410.776591</v>
       </c>
       <c r="D128">
-        <v>549794165.9114033</v>
-      </c>
-      <c r="G128">
-        <v>565481240.6119463</v>
+        <v>645688410.5156312</v>
+      </c>
+      <c r="E128">
+        <v>605005618.6188617</v>
+      </c>
+      <c r="I128">
+        <v>622268021.3906142</v>
       </c>
     </row>
     <row r="129">
@@ -6427,21 +7532,24 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>213390822.147658</v>
+        <v>785669970.6653789</v>
       </c>
       <c r="C129">
-        <v>1171834410.3724487</v>
+        <v>234819964.2079061</v>
       </c>
       <c r="D129">
-        <v>580641316.147658</v>
-      </c>
-      <c r="G129">
-        <v>542955762.965235</v>
+        <v>1289512414.5069575</v>
+      </c>
+      <c r="E129">
+        <v>638950502.6653789</v>
+      </c>
+      <c r="I129">
+        <v>597480489.2862265</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
   </ignoredErrors>
 </worksheet>
 </file>